--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="137">
   <si>
     <t>梦幻西游 · 支出明细表（黄色行为新增录入区）</t>
   </si>
@@ -79,6 +79,12 @@
   </si>
   <si>
     <t>主力账号</t>
+  </si>
+  <si>
+    <t>巫蛮儿</t>
+  </si>
+  <si>
+    <t>女儿村</t>
   </si>
   <si>
     <t/>
@@ -1701,9 +1707,15 @@
       <c r="A9" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="19"/>
+      <c r="B9" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="20">
+        <v>460</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="10" ht="16.5" customHeight="1" spans="1:4">
       <c r="A10" s="19" t="s">
@@ -1739,22 +1751,22 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:4">
       <c r="A14" s="21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C14" s="22">
         <f>SUM(C4:C13)</f>
-        <v>2676.9</v>
+        <v>3136.9</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1" spans="1:4">
       <c r="A15" s="16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
@@ -1762,136 +1774,136 @@
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="1:4">
       <c r="A16" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C16" s="8">
         <v>30</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:4">
       <c r="A17" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C17" s="8">
         <v>20</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:4">
       <c r="A18" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C18" s="8">
         <v>5</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:4">
       <c r="A19" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C19" s="8">
         <v>5</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:4">
       <c r="A20" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C20" s="8">
         <v>5</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="1:4">
       <c r="A21" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C21" s="8">
         <v>10</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" spans="1:4">
       <c r="A22" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C22" s="8">
         <v>25</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" spans="1:4">
       <c r="A23" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C23" s="8">
         <v>300</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1" spans="1:4">
       <c r="A24" s="19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C24" s="8">
         <v>125</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="1:4">
       <c r="A25" s="19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C25" s="20">
         <v>15</v>
@@ -1900,10 +1912,10 @@
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:4">
       <c r="A26" s="19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C26" s="20">
         <v>1.05</v>
@@ -1912,24 +1924,24 @@
     </row>
     <row r="27" ht="16.5" customHeight="1" spans="1:4">
       <c r="A27" s="19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C27" s="20">
         <v>25</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:4">
       <c r="A28" s="19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C28" s="20">
         <v>20</v>
@@ -1938,10 +1950,10 @@
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:4">
       <c r="A29" s="19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C29" s="20">
         <v>30</v>
@@ -1950,10 +1962,10 @@
     </row>
     <row r="30" ht="16.5" customHeight="1" spans="1:4">
       <c r="A30" s="19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C30" s="20">
         <v>290</v>
@@ -1964,10 +1976,10 @@
     </row>
     <row r="31" ht="16.5" customHeight="1" spans="1:4">
       <c r="A31" s="19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C31" s="20">
         <v>50</v>
@@ -1976,7 +1988,7 @@
     </row>
     <row r="32" ht="16.5" customHeight="1" spans="1:4">
       <c r="A32" s="19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="22"/>
@@ -1984,22 +1996,22 @@
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:4">
       <c r="A33" s="21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C33" s="22">
         <f>SUM(C16:C31)</f>
         <v>956.05</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1" spans="1:4">
       <c r="A34" s="16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -2007,176 +2019,176 @@
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="1:4">
       <c r="A35" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C35" s="8">
         <v>128</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="1:4">
       <c r="A36" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C36" s="8">
         <v>140</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" spans="1:4">
       <c r="A37" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C37" s="8">
         <v>120</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:4">
       <c r="A38" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C38" s="8">
         <v>168</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" spans="1:4">
       <c r="A39" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C39" s="8">
         <v>106</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" ht="16.5" customHeight="1" spans="1:4">
       <c r="A40" s="19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C40" s="20">
         <v>68.25</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:4">
       <c r="A41" s="19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C41" s="20">
         <v>65</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:4">
       <c r="A42" s="19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C42" s="20">
         <v>409</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" spans="1:4">
       <c r="A43" s="19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C43" s="20">
         <v>177</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" spans="1:4">
       <c r="A44" s="19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C44" s="20">
         <v>160</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" spans="1:4">
       <c r="A45" s="19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C45" s="20">
         <v>240</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1" spans="1:4">
       <c r="A46" s="21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C46" s="22">
         <f>SUM(C35:C45)</f>
         <v>1781.25</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:4">
       <c r="A47" s="16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
@@ -2184,49 +2196,49 @@
     </row>
     <row r="48" ht="16.5" customHeight="1" spans="1:4">
       <c r="A48" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C48" s="8">
         <v>20</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" ht="16.5" customHeight="1" spans="1:4">
       <c r="A49" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C49" s="8">
         <v>35</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" spans="1:4">
       <c r="A50" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C50" s="8">
         <v>40.5</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" ht="16.5" customHeight="1" spans="1:4">
       <c r="A51" s="19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B51" s="19"/>
       <c r="C51" s="20"/>
@@ -2234,7 +2246,7 @@
     </row>
     <row r="52" ht="16.5" customHeight="1" spans="1:4">
       <c r="A52" s="19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B52" s="19"/>
       <c r="C52" s="20"/>
@@ -2242,7 +2254,7 @@
     </row>
     <row r="53" ht="16.5" customHeight="1" spans="1:4">
       <c r="A53" s="19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B53" s="19"/>
       <c r="C53" s="20"/>
@@ -2250,7 +2262,7 @@
     </row>
     <row r="54" ht="16.5" customHeight="1" spans="1:4">
       <c r="A54" s="19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B54" s="19"/>
       <c r="C54" s="20"/>
@@ -2258,7 +2270,7 @@
     </row>
     <row r="55" ht="15" customHeight="1" spans="1:4">
       <c r="A55" s="19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B55" s="19"/>
       <c r="C55" s="20"/>
@@ -2266,44 +2278,44 @@
     </row>
     <row r="56" ht="15" spans="1:4">
       <c r="A56" s="21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C56" s="22">
         <f>SUM(C48:C55)</f>
         <v>95.5</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1"/>
     <row r="58" ht="18" spans="1:4">
       <c r="A58" s="23" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C58" s="11">
         <f>C14+C33+C46+C56</f>
-        <v>5509.7</v>
+        <v>5969.7</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" ht="16.5" customHeight="1"/>
     <row r="60" ht="16.5" customHeight="1" spans="1:4">
       <c r="A60" s="14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:4">
       <c r="A61" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2334,15 +2346,15 @@
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -2353,7 +2365,7 @@
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:4">
       <c r="A3" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -2361,176 +2373,176 @@
     </row>
     <row r="4" ht="16.5" customHeight="1" spans="1:4">
       <c r="A4" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C4" s="8">
         <v>85.5</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="1:4">
       <c r="A5" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C5" s="20">
         <v>161.5</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:4">
       <c r="A6" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C6" s="20">
         <v>123.5</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="1:4">
       <c r="A7" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C7" s="20">
         <v>9.5</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" spans="1:4">
       <c r="A8" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C8" s="20">
         <v>115</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1" spans="1:4">
       <c r="A9" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C9" s="20">
         <v>9.5</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" ht="16.5" customHeight="1" spans="1:4">
       <c r="A10" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C10" s="20">
         <v>133</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" ht="16.5" customHeight="1" spans="1:4">
       <c r="A11" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C11" s="20">
         <v>66.5</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:4">
       <c r="A12" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C12" s="20">
         <v>14.5</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="1:4">
       <c r="A13" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C13" s="20">
         <v>14.5</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:4">
       <c r="A14" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C14" s="20">
         <v>9.5</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:4">
       <c r="A15" s="21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C15" s="22">
         <f>SUM(C4:C14)</f>
         <v>742.5</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1" spans="1:4">
       <c r="A16" s="16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -2538,289 +2550,289 @@
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:4">
       <c r="A17" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C17" s="8">
         <v>202</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:4">
       <c r="A18" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C18" s="8">
         <v>67.45</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:4">
       <c r="A19" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C19" s="8">
         <v>67.45</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:4">
       <c r="A20" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C20" s="8">
         <v>66.78</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="1:4">
       <c r="A21" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C21" s="8">
         <v>66.78</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" spans="1:4">
       <c r="A22" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C22" s="20">
         <v>66.02</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" spans="1:4">
       <c r="A23" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C23" s="20">
         <v>65.55</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1" spans="1:4">
       <c r="A24" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C24" s="20">
         <v>66.02</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="1:4">
       <c r="A25" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C25" s="20">
         <v>69.2</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:4">
       <c r="A26" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C26" s="20">
         <v>68</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1" spans="1:4">
       <c r="A27" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C27" s="20">
         <v>41</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:4">
       <c r="A28" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C28" s="20">
         <v>67.7</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:4">
       <c r="A29" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C29" s="20">
         <v>68</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1" spans="1:4">
       <c r="A30" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C30" s="20">
         <v>41.82</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:4">
       <c r="A31" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C31" s="20">
         <v>197</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:4">
       <c r="A32" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C32" s="20">
         <v>25.84</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:4">
       <c r="A33" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C33" s="20">
         <v>191.9</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:4">
       <c r="A34" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C34" s="20">
         <v>111</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" spans="1:4">
       <c r="A35" s="21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C35" s="22">
         <f>SUM(C17:C34)</f>
         <v>1549.51</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" spans="1:4">
       <c r="A37" s="21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C37" s="22">
         <f>C15+C35</f>
         <v>2292.01</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:4">
       <c r="A39" s="14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2848,89 +2860,89 @@
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B3" s="5">
         <f>支出明细表!C58</f>
-        <v>5509.7</v>
+        <v>5969.7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" ht="16.5" customHeight="1" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B4" s="8">
         <f>游戏变现收入明细表!C37</f>
         <v>2292.01</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3">
       <c r="A5" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B5" s="11">
         <f>B3-B4</f>
-        <v>3217.69</v>
+        <v>3677.69</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:3">
       <c r="A7" s="13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:3">
       <c r="A8" s="14" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:3">
       <c r="A9" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:3">
       <c r="A10" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:3">
       <c r="A11" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:3">
       <c r="A12" s="14" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:3">
       <c r="A14" s="15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17775" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="20085" windowHeight="9240" firstSheet="1"/>
   </bookViews>
   <sheets>
     <sheet name="支出明细表" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="141">
   <si>
     <t>梦幻西游 · 支出明细表（黄色行为新增录入区）</t>
   </si>
@@ -157,6 +157,9 @@
   </si>
   <si>
     <t>9月月卡</t>
+  </si>
+  <si>
+    <t>9月21点卡</t>
   </si>
   <si>
     <t>点卡小计</t>
@@ -1606,7 +1609,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1999,358 +2002,370 @@
       <c r="A32" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="21"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="21"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" spans="1:4">
-      <c r="A33" s="21" t="s">
+      <c r="B32" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="20">
+        <v>25</v>
+      </c>
+      <c r="D32" s="19"/>
+    </row>
+    <row r="33" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A33" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="21"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="21"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" spans="1:4">
+      <c r="A34" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="22">
-        <f>SUM(C16:C31)</f>
-        <v>956.05</v>
-      </c>
-      <c r="D33" s="21" t="s">
+      <c r="B34" s="21" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="34" ht="26" customHeight="1" spans="1:4">
-      <c r="A34" s="16" t="s">
+      <c r="C34" s="22">
+        <f>SUM(C16:C32)</f>
+        <v>981.05</v>
+      </c>
+      <c r="D34" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="18"/>
-    </row>
-    <row r="35" ht="16.5" customHeight="1" spans="1:4">
-      <c r="A35" s="9" t="s">
+    </row>
+    <row r="35" ht="26" customHeight="1" spans="1:4">
+      <c r="A35" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C35" s="8">
-        <v>128</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="18"/>
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="1:4">
       <c r="A36" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B36" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" s="8">
+        <v>128</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>47</v>
-      </c>
-      <c r="C36" s="8">
-        <v>140</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" spans="1:4">
       <c r="A37" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B37" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="8">
+        <v>140</v>
+      </c>
+      <c r="D37" s="9" t="s">
         <v>49</v>
-      </c>
-      <c r="C37" s="8">
-        <v>120</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:4">
       <c r="A38" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>50</v>
       </c>
       <c r="C38" s="8">
-        <v>168</v>
+        <v>120</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" spans="1:4">
       <c r="A39" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B39" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="8">
+        <v>168</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C39" s="8">
+    </row>
+    <row r="40" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A40" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="8">
         <v>106</v>
       </c>
-      <c r="D39" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="40" ht="16.5" customHeight="1" spans="1:4">
-      <c r="A40" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" s="19" t="s">
+      <c r="D40" s="9" t="s">
         <v>54</v>
-      </c>
-      <c r="C40" s="20">
-        <v>68.25</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:4">
       <c r="A41" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B41" s="19" t="s">
         <v>55</v>
       </c>
       <c r="C41" s="20">
-        <v>65</v>
+        <v>68.25</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:4">
       <c r="A42" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" s="19" t="s">
         <v>56</v>
       </c>
       <c r="C42" s="20">
-        <v>409</v>
-      </c>
-      <c r="D42" s="19" t="s">
-        <v>57</v>
+        <v>65</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" spans="1:4">
       <c r="A43" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B43" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="20">
+        <v>409</v>
+      </c>
+      <c r="D43" s="19" t="s">
         <v>58</v>
-      </c>
-      <c r="C43" s="20">
-        <v>177</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" spans="1:4">
       <c r="A44" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B44" s="19" t="s">
         <v>59</v>
       </c>
       <c r="C44" s="20">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1" spans="1:4">
       <c r="A45" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" s="19" t="s">
         <v>60</v>
       </c>
       <c r="C45" s="20">
+        <v>160</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A46" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C46" s="20">
         <v>210</v>
       </c>
-      <c r="D45" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" spans="1:4">
-      <c r="A46" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="19" t="s">
+      <c r="D46" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C46" s="20">
+    </row>
+    <row r="47" ht="15" customHeight="1" spans="1:4">
+      <c r="A47" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" s="20">
         <v>240</v>
       </c>
-      <c r="D46" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" ht="26" customHeight="1" spans="1:4">
-      <c r="A47" s="21" t="s">
+      <c r="D47" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1" spans="1:4">
+      <c r="A48" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B47" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C47" s="22">
-        <f>SUM(C35:C46)</f>
+      <c r="B48" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" s="22">
+        <f>SUM(C36:C47)</f>
         <v>1991.25</v>
       </c>
-      <c r="D47" s="21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" ht="16.5" customHeight="1" spans="1:4">
-      <c r="A48" s="16" t="s">
+      <c r="D48" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="18"/>
     </row>
     <row r="49" ht="16.5" customHeight="1" spans="1:4">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B49" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C49" s="8">
-        <v>20</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>68</v>
-      </c>
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="18"/>
     </row>
     <row r="50" ht="16.5" customHeight="1" spans="1:4">
       <c r="A50" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B50" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" s="8">
+        <v>20</v>
+      </c>
+      <c r="D50" s="9" t="s">
         <v>69</v>
-      </c>
-      <c r="C50" s="8">
-        <v>35</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="51" ht="16.5" customHeight="1" spans="1:4">
       <c r="A51" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>70</v>
       </c>
       <c r="C51" s="8">
+        <v>35</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A52" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="8">
         <v>40.5</v>
       </c>
-      <c r="D51" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="52" ht="16.5" customHeight="1" spans="1:4">
-      <c r="A52" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="B52" s="19" t="s">
+      <c r="D52" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="C52" s="20">
-        <v>10</v>
-      </c>
-      <c r="D52" s="19" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="53" ht="16.5" customHeight="1" spans="1:4">
       <c r="A53" s="19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B53" s="19" t="s">
         <v>73</v>
       </c>
       <c r="C53" s="20">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" ht="16.5" customHeight="1" spans="1:4">
       <c r="A54" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="B54" s="19"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="19"/>
+        <v>67</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C54" s="20">
+        <v>35</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="55" ht="16.5" customHeight="1" spans="1:4">
       <c r="A55" s="19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B55" s="19"/>
       <c r="C55" s="20"/>
       <c r="D55" s="19"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:4">
+    <row r="56" ht="16.5" customHeight="1" spans="1:4">
       <c r="A56" s="19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B56" s="19"/>
       <c r="C56" s="20"/>
       <c r="D56" s="19"/>
     </row>
     <row r="57" ht="15" customHeight="1" spans="1:4">
-      <c r="A57" s="21" t="s">
+      <c r="A57" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57" s="19"/>
+      <c r="C57" s="20"/>
+      <c r="D57" s="19"/>
+    </row>
+    <row r="58" ht="15" customHeight="1" spans="1:4">
+      <c r="A58" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="C57" s="22">
-        <f>SUM(C49:C56)</f>
+      <c r="B58" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C58" s="22">
+        <f>SUM(C50:C57)</f>
         <v>140.5</v>
       </c>
-      <c r="D57" s="21" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1"/>
-    <row r="59" ht="18" customHeight="1" spans="1:4">
-      <c r="A59" s="23" t="s">
+      <c r="D58" s="21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1"/>
+    <row r="60" ht="18" customHeight="1" spans="1:4">
+      <c r="A60" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B59" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="C59" s="11">
-        <f>C14+C33+C47+C57</f>
-        <v>6224.7</v>
-      </c>
-      <c r="D59" s="23" t="s">
+      <c r="B60" s="23" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="60" ht="16.5" customHeight="1"/>
-    <row r="61" ht="16.5" customHeight="1" spans="1:4">
-      <c r="A61" s="14" t="s">
+      <c r="C60" s="11">
+        <f>C14+C34+C48+C58</f>
+        <v>6249.7</v>
+      </c>
+      <c r="D60" s="23" t="s">
         <v>78</v>
       </c>
     </row>
+    <row r="61" ht="16.5" customHeight="1"/>
     <row r="62" ht="16.5" customHeight="1" spans="1:4">
       <c r="A62" s="14" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A63" s="14" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2358,9 +2373,9 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A62:D62"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2381,15 +2396,15 @@
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -2400,7 +2415,7 @@
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:4">
       <c r="A3" s="16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -2408,156 +2423,156 @@
     </row>
     <row r="4" ht="16.5" customHeight="1" spans="1:4">
       <c r="A4" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" s="8">
         <v>85.5</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="1:4">
       <c r="A5" s="19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" s="20">
         <v>161.5</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:4">
       <c r="A6" s="19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" s="20">
         <v>123.5</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="1:4">
       <c r="A7" s="19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" s="20">
         <v>9.5</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" spans="1:4">
       <c r="A8" s="19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C8" s="20">
         <v>115</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1" spans="1:4">
       <c r="A9" s="19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C9" s="20">
         <v>9.5</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" ht="16.5" customHeight="1" spans="1:4">
       <c r="A10" s="19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C10" s="20">
         <v>133</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" ht="16.5" customHeight="1" spans="1:4">
       <c r="A11" s="19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C11" s="20">
         <v>66.5</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:4">
       <c r="A12" s="19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C12" s="20">
         <v>14.5</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="1:4">
       <c r="A13" s="19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C13" s="20">
         <v>14.5</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:4">
       <c r="A14" s="19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C14" s="20">
         <v>9.5</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:4">
@@ -2565,7 +2580,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C15" s="22">
         <f>SUM(C4:C14)</f>
@@ -2577,7 +2592,7 @@
     </row>
     <row r="16" ht="26" customHeight="1" spans="1:4">
       <c r="A16" s="16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -2585,254 +2600,254 @@
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:4">
       <c r="A17" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C17" s="8">
         <v>202</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:4">
       <c r="A18" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C18" s="8">
         <v>67.45</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:4">
       <c r="A19" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C19" s="8">
         <v>67.45</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:4">
       <c r="A20" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C20" s="8">
         <v>66.78</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="1:4">
       <c r="A21" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C21" s="8">
         <v>66.78</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" spans="1:4">
       <c r="A22" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C22" s="20">
         <v>66.02</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" spans="1:4">
       <c r="A23" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C23" s="20">
         <v>65.55</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1" spans="1:4">
       <c r="A24" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C24" s="20">
         <v>66.02</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="1:4">
       <c r="A25" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C25" s="20">
         <v>69.2</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:4">
       <c r="A26" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C26" s="20">
         <v>68</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1" spans="1:4">
       <c r="A27" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C27" s="20">
         <v>41</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:4">
       <c r="A28" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C28" s="20">
         <v>67.7</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:4">
       <c r="A29" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C29" s="20">
         <v>68</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1" spans="1:4">
       <c r="A30" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C30" s="20">
         <v>41.82</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:4">
       <c r="A31" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C31" s="20">
         <v>197</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:4">
       <c r="A32" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C32" s="20">
         <v>25.84</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1" spans="1:4">
       <c r="A33" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C33" s="20">
         <v>191.9</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" spans="1:4">
       <c r="A34" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C34" s="20">
         <v>111</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" spans="1:4">
@@ -2840,7 +2855,7 @@
         <v>17</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C35" s="22">
         <f>SUM(C17:C34)</f>
@@ -2855,19 +2870,19 @@
         <v>17</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C37" s="22">
         <f>C15+C35</f>
         <v>2292.01</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" spans="1:4">
       <c r="A39" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -2895,84 +2910,84 @@
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B3" s="5">
-        <f>支出明细表!C59</f>
-        <v>6224.7</v>
+        <f>支出明细表!C60</f>
+        <v>6249.7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" ht="16.5" customHeight="1" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="8">
         <f>游戏变现收入明细表!C37</f>
         <v>2292.01</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3">
       <c r="A5" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B5" s="11">
         <f>B3-B4</f>
-        <v>3932.69</v>
+        <v>3957.69</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:3">
       <c r="A7" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:3">
       <c r="A8" s="14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:3">
       <c r="A9" s="14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:3">
       <c r="A10" s="14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:3">
       <c r="A11" s="14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:3">
       <c r="A12" s="14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:3">

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -1251,7 +1251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1821,51 +1821,47 @@
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="21" t="inlineStr"/>
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>点卡相关</t>
+        </is>
+      </c>
       <c r="B34" s="21" t="inlineStr">
         <is>
+          <t>9月23点卡</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="D34" s="21" t="n"/>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="21" t="inlineStr"/>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
           <t>点卡小计</t>
         </is>
       </c>
-      <c r="C34" s="22">
-        <f>SUM(C16:C32)</f>
+      <c r="C35" s="22">
+        <f>SUM(C16:C33)</f>
         <v/>
       </c>
-      <c r="D34" s="21" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr">
         <is>
           <t>全部点卡充值合计</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
+    <row r="36" ht="16.5" customHeight="1">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>▌召唤兽采购</t>
         </is>
       </c>
-      <c r="B35" s="17" t="n"/>
-      <c r="C35" s="17" t="n"/>
-      <c r="D35" s="18" t="n"/>
-    </row>
-    <row r="36" ht="16.5" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>召唤兽采购</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>蓝书力宠画魂</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="n">
-        <v>128</v>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>力宠（已卖出）</t>
-        </is>
-      </c>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="18" t="n"/>
     </row>
     <row r="37" ht="16.5" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
@@ -1875,15 +1871,15 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>力宠蝴蝶仙子</t>
+          <t>蓝书力宠画魂</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>力宠</t>
+          <t>力宠（已卖出）</t>
         </is>
       </c>
     </row>
@@ -1895,15 +1891,15 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>力宠吸血鬼</t>
+          <t>力宠蝴蝶仙子</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>力宠（已卖出）</t>
+          <t>力宠</t>
         </is>
       </c>
     </row>
@@ -1915,15 +1911,15 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>力宠龙鲤</t>
+          <t>力宠吸血鬼</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>168</v>
+        <v>120</v>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>力宠 （已卖出）</t>
+          <t>力宠（已卖出）</t>
         </is>
       </c>
     </row>
@@ -1935,35 +1931,35 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
+          <t>力宠龙鲤</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>168</v>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>力宠 （已卖出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16.5" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>召唤兽采购</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
           <t>购入法宠</t>
         </is>
       </c>
-      <c r="C40" s="8" t="n">
+      <c r="C41" s="8" t="n">
         <v>106</v>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>法宠（后续卖出）</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16.5" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>召唤兽采购</t>
-        </is>
-      </c>
-      <c r="B41" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79龙鲤 </t>
-        </is>
-      </c>
-      <c r="C41" s="20" t="n">
-        <v>68.25</v>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>力宠</t>
         </is>
       </c>
     </row>
@@ -1975,11 +1971,11 @@
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
-          <t>79龙鲤 2</t>
+          <t xml:space="preserve">79龙鲤 </t>
         </is>
       </c>
       <c r="C42" s="20" t="n">
-        <v>65</v>
+        <v>68.25</v>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
@@ -1995,15 +1991,15 @@
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
-          <t>须弥画魂高魔心带套0903</t>
+          <t>79龙鲤 2</t>
         </is>
       </c>
       <c r="C43" s="20" t="n">
-        <v>409</v>
-      </c>
-      <c r="D43" s="19" t="inlineStr">
-        <is>
-          <t>法宠</t>
+        <v>65</v>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>力宠</t>
         </is>
       </c>
     </row>
@@ -2015,15 +2011,15 @@
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">龙鲤0908 </t>
+          <t>须弥画魂高魔心带套0903</t>
         </is>
       </c>
       <c r="C44" s="20" t="n">
-        <v>177</v>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>力宠</t>
+        <v>409</v>
+      </c>
+      <c r="D44" s="19" t="inlineStr">
+        <is>
+          <t>法宠</t>
         </is>
       </c>
     </row>
@@ -2035,11 +2031,11 @@
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
-          <t>三技能女娲0908</t>
+          <t xml:space="preserve">龙鲤0908 </t>
         </is>
       </c>
       <c r="C45" s="20" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
@@ -2055,15 +2051,15 @@
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>雷鸟人须弥 9月20</t>
+          <t>三技能女娲0908</t>
         </is>
       </c>
       <c r="C46" s="20" t="n">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>须弥法宠</t>
+          <t>力宠</t>
         </is>
       </c>
     </row>
@@ -2075,64 +2071,64 @@
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
+          <t>雷鸟人须弥 9月20</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="n">
+        <v>210</v>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>须弥法宠</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>召唤兽采购</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
           <t>雷鸟人须弥 9月11</t>
         </is>
       </c>
-      <c r="C47" s="20" t="n">
+      <c r="C48" s="20" t="n">
         <v>240</v>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>须弥法宠</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="26" customHeight="1">
-      <c r="A48" s="21" t="inlineStr"/>
-      <c r="B48" s="21" t="inlineStr">
+    <row r="49" ht="16.5" customHeight="1">
+      <c r="A49" s="21" t="inlineStr"/>
+      <c r="B49" s="21" t="inlineStr">
         <is>
           <t>购宠小计</t>
         </is>
       </c>
-      <c r="C48" s="22">
-        <f>SUM(C36:C47)</f>
+      <c r="C49" s="22">
+        <f>SUM(C37:C48)</f>
         <v/>
       </c>
-      <c r="D48" s="21" t="inlineStr">
+      <c r="D49" s="21" t="inlineStr">
         <is>
           <t>宠物采购总花费</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1">
-      <c r="A49" s="16" t="inlineStr">
+    <row r="50" ht="16.5" customHeight="1">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>▌装备采购</t>
         </is>
       </c>
-      <c r="B49" s="17" t="n"/>
-      <c r="C49" s="17" t="n"/>
-      <c r="D49" s="18" t="n"/>
-    </row>
-    <row r="50" ht="16.5" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>装备采购</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>主号武器</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>主力角色装备</t>
-        </is>
-      </c>
+      <c r="B50" s="17" t="n"/>
+      <c r="C50" s="17" t="n"/>
+      <c r="D50" s="18" t="n"/>
     </row>
     <row r="51" ht="16.5" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
@@ -2142,11 +2138,11 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>主号鞋子</t>
+          <t>主号武器</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
@@ -2162,35 +2158,35 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
+          <t>主号鞋子</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>主力角色装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16.5" customHeight="1">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>装备采购</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
           <t>4 角色 100 级国标武器</t>
         </is>
       </c>
-      <c r="C52" s="8" t="n">
+      <c r="C53" s="8" t="n">
         <v>40.5</v>
       </c>
-      <c r="D52" s="9" t="inlineStr">
+      <c r="D53" s="9" t="inlineStr">
         <is>
           <t>其余小号武器</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="16.5" customHeight="1">
-      <c r="A53" s="19" t="inlineStr">
-        <is>
-          <t>装备采购</t>
-        </is>
-      </c>
-      <c r="B53" s="19" t="inlineStr">
-        <is>
-          <t>后排灵饰109</t>
-        </is>
-      </c>
-      <c r="C53" s="20" t="n">
-        <v>109</v>
-      </c>
-      <c r="D53" s="19" t="inlineStr">
-        <is>
-          <t>装备采购</t>
         </is>
       </c>
     </row>
@@ -2202,11 +2198,11 @@
       </c>
       <c r="B54" s="19" t="inlineStr">
         <is>
-          <t>风伯套装48</t>
+          <t>后排灵饰109</t>
         </is>
       </c>
       <c r="C54" s="20" t="n">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="D54" s="19" t="inlineStr">
         <is>
@@ -2222,11 +2218,11 @@
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
-          <t>吸血鬼鞋子（套牢）</t>
+          <t>风伯套装48</t>
         </is>
       </c>
       <c r="C55" s="20" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="D55" s="19" t="inlineStr">
         <is>
@@ -2242,11 +2238,11 @@
       </c>
       <c r="B56" s="19" t="inlineStr">
         <is>
-          <t>国标武器</t>
+          <t>吸血鬼鞋子（套牢）</t>
         </is>
       </c>
       <c r="C56" s="20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D56" s="19" t="inlineStr">
         <is>
@@ -2260,55 +2256,75 @@
           <t>装备采购</t>
         </is>
       </c>
-      <c r="B57" s="19" t="n"/>
-      <c r="C57" s="20" t="n"/>
-      <c r="D57" s="19" t="n"/>
+      <c r="B57" s="19" t="inlineStr">
+        <is>
+          <t>国标武器</t>
+        </is>
+      </c>
+      <c r="C57" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D57" s="19" t="inlineStr">
+        <is>
+          <t>装备采购</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="21" t="inlineStr"/>
-      <c r="B58" s="21" t="inlineStr">
+      <c r="A58" s="19" t="inlineStr">
+        <is>
+          <t>装备采购</t>
+        </is>
+      </c>
+      <c r="B58" s="19" t="n"/>
+      <c r="C58" s="20" t="n"/>
+      <c r="D58" s="19" t="n"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="21" t="inlineStr"/>
+      <c r="B59" s="21" t="inlineStr">
         <is>
           <t>装备小计</t>
         </is>
       </c>
-      <c r="C58" s="22">
-        <f>SUM(C50:C57)</f>
+      <c r="C59" s="22">
+        <f>SUM(C51:C58)</f>
         <v/>
       </c>
-      <c r="D58" s="21" t="inlineStr">
+      <c r="D59" s="21" t="inlineStr">
         <is>
           <t>装备总花费</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1"/>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="24" t="inlineStr"/>
-      <c r="B60" s="24" t="inlineStr">
+    <row r="60" ht="18" customHeight="1"/>
+    <row r="61" ht="16.5" customHeight="1">
+      <c r="A61" s="24" t="n"/>
+      <c r="B61" s="24" t="inlineStr">
         <is>
           <t>全部支出合计</t>
         </is>
       </c>
-      <c r="C60" s="11">
-        <f>C14+C34+C48+C58</f>
+      <c r="C61" s="11">
+        <f>C14+C35+C49+C59</f>
         <v/>
       </c>
-      <c r="D60" s="24" t="inlineStr">
+      <c r="D61" s="24" t="inlineStr">
         <is>
           <t>所有板块总支出</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="16.5" customHeight="1"/>
-    <row r="62" ht="16.5" customHeight="1">
-      <c r="A62" s="14" t="inlineStr">
-        <is>
-          <t>📌 操作说明：在黄色底纹行录入新支出，金额填入 C 列，小计和合计自动更新。</t>
-        </is>
-      </c>
-    </row>
+    <row r="62" ht="16.5" customHeight="1"/>
     <row r="63" ht="16.5" customHeight="1">
       <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>📌 操作说明：在黄色底纹行录入新支出，金额填入 C 列，小计和合计自动更新。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
         <is>
           <t>📌 如需更多行：右键插入行 → 从上方黄色行复制格式即可。</t>
         </is>
@@ -2317,11 +2333,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A50:D50"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A36:D36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2333,7 +2349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3005,41 +3021,57 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="23" t="n"/>
-      <c r="B36" s="23" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>物资变现</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>卖古代瑞兽胚子 9月23</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D36" s="19" t="n"/>
+    </row>
+    <row r="37" ht="16.5" customHeight="1">
+      <c r="A37" s="23" t="n"/>
+      <c r="B37" s="23" t="inlineStr">
         <is>
           <t>物资小计</t>
         </is>
       </c>
-      <c r="C36" s="23">
-        <f>SUM(C17:C35)</f>
+      <c r="C37" s="23">
+        <f>SUM(C17:C36)</f>
         <v/>
       </c>
-      <c r="D36" s="23" t="n"/>
-    </row>
-    <row r="37" ht="16.5" customHeight="1">
-      <c r="A37" s="21" t="inlineStr"/>
-      <c r="B37" s="21" t="n"/>
-      <c r="C37" s="22" t="n"/>
-      <c r="D37" s="21" t="inlineStr">
+      <c r="D37" s="23" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr"/>
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>所有回款合计</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
+    <row r="39" ht="16.5" customHeight="1">
+      <c r="B39" t="inlineStr">
         <is>
           <t>全部变现总收入</t>
         </is>
       </c>
-      <c r="C38">
-        <f>C15+C36</f>
+      <c r="C39">
+        <f>C15+C37</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1">
-      <c r="A39" s="14" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>📌 操作说明：在黄色底纹行录入新收入，金额填入 C 列，小计和合计自动更新。</t>
         </is>
@@ -3048,9 +3080,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A39:D39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="B3" s="5">
-        <f>支出明细表!C60</f>
+        <f>支出明细表!C61</f>
         <v/>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="B4" s="8">
-        <f>游戏变现收入明细表!C38</f>
+        <f>游戏变现收入明细表!C39</f>
         <v/>
       </c>
       <c r="C4" s="9" t="inlineStr">

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="29">
+  <fonts count="34">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -229,8 +229,26 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="41">
+  <fills count="47">
     <fill>
       <patternFill/>
     </fill>
@@ -471,8 +489,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCDD2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -637,6 +685,64 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -785,7 +891,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -839,6 +945,24 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="42" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="43" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="32" fillId="43" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="44" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="45" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="33" fillId="45" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="46" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="31" fillId="46" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1251,7 +1375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1260,1084 +1384,1123 @@
     <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>梦幻西游 · 支出明细表（黄色行为新增录入区）</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>分类</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>明细项目</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="26" t="inlineStr">
         <is>
           <t>金额 (元)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="26" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>▌角色账号购置</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n"/>
-      <c r="C3" s="17" t="n"/>
-      <c r="D3" s="18" t="n"/>
-    </row>
-    <row r="4" ht="16.5" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="B3" s="37" t="n"/>
+      <c r="C3" s="37" t="n"/>
+      <c r="D3" s="38" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>角色账号购置</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>巨魔王一号</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="30" t="n">
         <v>391.9</v>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>男角色</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>角色账号购置</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>骨精灵</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="30" t="n">
         <v>400</v>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>女角色</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>角色账号购置</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>杀破狼</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="30" t="n">
         <v>519</v>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>男角色</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>角色账号购置</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>巨魔王二号</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="30" t="n">
         <v>500</v>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>男角色</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>角色账号购置</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>主号男角色</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="30" t="n">
         <v>866</v>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>主力账号</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>角色账号购置</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>巫蛮儿</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="30" t="n">
         <v>460</v>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>女儿村</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>角色账号购置</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="19" t="n"/>
-    </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>角色账号购置</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="n"/>
-      <c r="C11" s="20" t="n"/>
-      <c r="D11" s="19" t="n"/>
-    </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>角色账号购置</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="19" t="n"/>
-    </row>
-    <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>角色账号购置</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="n"/>
-      <c r="C13" s="20" t="n"/>
-      <c r="D13" s="19" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="21" t="inlineStr"/>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>账号小计</t>
-        </is>
-      </c>
-      <c r="C14" s="22">
-        <f>SUM(C4:C13)</f>
+    <row r="10">
+      <c r="A10" s="31" t="n"/>
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="31" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n"/>
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="31" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="31" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n"/>
+      <c r="B13" s="31" t="n"/>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="31" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n"/>
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="32" t="n"/>
+      <c r="D14" s="31" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="n"/>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>角色小计</t>
+        </is>
+      </c>
+      <c r="C15" s="34">
+        <f>SUM(C4:C14)</f>
         <v/>
       </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>5 个账号 + 新增合计</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="D15" s="33" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>▌点卡相关</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="18" t="n"/>
-    </row>
-    <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="37" t="n"/>
+      <c r="D17" s="38" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>30 元点卡</t>
         </is>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C18" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>原拆分点卡</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>20 元点卡</t>
         </is>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C19" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>原拆分点卡</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>5 元点卡</t>
         </is>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C20" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>原拆分点卡</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>5 元点卡</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C21" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>原拆分点卡</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B22" s="29" t="inlineStr">
         <is>
           <t>5 元点卡</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C22" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D22" s="29" t="inlineStr">
         <is>
           <t>原拆分点卡</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>10 元补充点卡</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C23" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>漏算补充</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>25 元追加点卡</t>
         </is>
       </c>
-      <c r="C22" s="8" t="n">
+      <c r="C24" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D24" s="29" t="inlineStr">
         <is>
           <t>后期新增</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>300 元月卡</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C25" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D25" s="29" t="inlineStr">
         <is>
           <t>第一轮月卡</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>小号点卡第一轮</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n">
+      <c r="C26" s="30" t="n">
         <v>125</v>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D26" s="29" t="inlineStr">
         <is>
           <t>小号点卡 30*5支付优惠</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t>8月21点卡</t>
         </is>
       </c>
-      <c r="C25" s="20" t="n">
+      <c r="C27" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="D25" s="19" t="n"/>
-    </row>
-    <row r="26" ht="16.5" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="D27" s="29" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B28" s="29" t="inlineStr">
         <is>
           <t>8月24点卡</t>
         </is>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C28" s="30" t="n">
         <v>1.05</v>
       </c>
-      <c r="D26" s="19" t="n"/>
-    </row>
-    <row r="27" ht="16.5" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="D28" s="29" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>8月27点卡</t>
         </is>
       </c>
-      <c r="C27" s="20" t="n">
+      <c r="C29" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="19" t="inlineStr">
+      <c r="D29" s="29" t="inlineStr">
         <is>
           <t>小号</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B30" s="29" t="inlineStr">
         <is>
           <t>8月26点卡</t>
         </is>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C30" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="D28" s="19" t="n"/>
-    </row>
-    <row r="29" ht="16.5" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="D30" s="29" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B31" s="29" t="inlineStr">
         <is>
           <t>8月30点卡</t>
         </is>
       </c>
-      <c r="C29" s="20" t="n">
+      <c r="C31" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="D29" s="19" t="n"/>
-    </row>
-    <row r="30" ht="16.5" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="D31" s="29" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr">
+      <c r="B32" s="29" t="inlineStr">
         <is>
           <t>9月月卡</t>
         </is>
       </c>
-      <c r="C30" s="20" t="n">
+      <c r="C32" s="30" t="n">
         <v>290</v>
       </c>
-      <c r="D30" s="19" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" ht="16.5" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
+      <c r="D32" s="29" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>8月30点卡</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="n">
+      <c r="B33" s="29" t="inlineStr">
+        <is>
+          <t>8月30点卡50</t>
+        </is>
+      </c>
+      <c r="C33" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="D31" s="19" t="n"/>
-    </row>
-    <row r="32" ht="16.5" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="D33" s="29" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B32" s="19" t="inlineStr">
+      <c r="B34" s="29" t="inlineStr">
         <is>
           <t>9月21点卡</t>
         </is>
       </c>
-      <c r="C32" s="20" t="n">
+      <c r="C34" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="D32" s="19" t="n"/>
-    </row>
-    <row r="33" ht="16.5" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
+      <c r="D34" s="29" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B35" s="29" t="inlineStr">
         <is>
           <t>9月22点卡</t>
         </is>
       </c>
-      <c r="C33" s="22" t="n">
+      <c r="C35" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="D33" s="21" t="inlineStr">
+      <c r="D35" s="29" t="inlineStr">
         <is>
           <t>4个号补</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="19" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="29" t="inlineStr">
         <is>
           <t>点卡相关</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B36" s="29" t="inlineStr">
         <is>
           <t>9月23点卡</t>
         </is>
       </c>
-      <c r="C34" s="22" t="n">
+      <c r="C36" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="D34" s="21" t="n"/>
-    </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="21" t="inlineStr"/>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="D36" s="29" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="n"/>
+      <c r="B37" s="31" t="n"/>
+      <c r="C37" s="32" t="n"/>
+      <c r="D37" s="31" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="31" t="n"/>
+      <c r="B38" s="31" t="n"/>
+      <c r="C38" s="32" t="n"/>
+      <c r="D38" s="31" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="31" t="n"/>
+      <c r="B39" s="31" t="n"/>
+      <c r="C39" s="32" t="n"/>
+      <c r="D39" s="31" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="31" t="n"/>
+      <c r="B40" s="31" t="n"/>
+      <c r="C40" s="32" t="n"/>
+      <c r="D40" s="31" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="31" t="n"/>
+      <c r="B41" s="31" t="n"/>
+      <c r="C41" s="32" t="n"/>
+      <c r="D41" s="31" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="33" t="n"/>
+      <c r="B42" s="33" t="inlineStr">
         <is>
           <t>点卡小计</t>
         </is>
       </c>
-      <c r="C35" s="22">
-        <f>SUM(C16:C33)</f>
+      <c r="C42" s="34">
+        <f>SUM(C18:C41)</f>
         <v/>
       </c>
-      <c r="D35" s="21" t="inlineStr">
-        <is>
-          <t>全部点卡充值合计</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="16.5" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="D42" s="33" t="n"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="27" t="inlineStr">
         <is>
           <t>▌召唤兽采购</t>
         </is>
       </c>
-      <c r="B36" s="17" t="n"/>
-      <c r="C36" s="17" t="n"/>
-      <c r="D36" s="18" t="n"/>
-    </row>
-    <row r="37" ht="16.5" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="B44" s="37" t="n"/>
+      <c r="C44" s="37" t="n"/>
+      <c r="D44" s="38" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="29" t="inlineStr">
         <is>
           <t>召唤兽采购</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B45" s="29" t="inlineStr">
         <is>
           <t>蓝书力宠画魂</t>
         </is>
       </c>
-      <c r="C37" s="8" t="n">
+      <c r="C45" s="30" t="n">
         <v>128</v>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D45" s="29" t="inlineStr">
         <is>
           <t>力宠（已卖出）</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="29" t="inlineStr">
         <is>
           <t>召唤兽采购</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B46" s="29" t="inlineStr">
         <is>
           <t>力宠蝴蝶仙子</t>
         </is>
       </c>
-      <c r="C38" s="8" t="n">
+      <c r="C46" s="30" t="n">
         <v>140</v>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D46" s="29" t="inlineStr">
         <is>
           <t>力宠</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="29" t="inlineStr">
         <is>
           <t>召唤兽采购</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B47" s="29" t="inlineStr">
         <is>
           <t>力宠吸血鬼</t>
         </is>
       </c>
-      <c r="C39" s="8" t="n">
+      <c r="C47" s="30" t="n">
         <v>120</v>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D47" s="29" t="inlineStr">
         <is>
           <t>力宠（已卖出）</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="29" t="inlineStr">
         <is>
           <t>召唤兽采购</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B48" s="29" t="inlineStr">
         <is>
           <t>力宠龙鲤</t>
         </is>
       </c>
-      <c r="C40" s="8" t="n">
+      <c r="C48" s="30" t="n">
         <v>168</v>
       </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>力宠 （已卖出）</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16.5" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="D48" s="29" t="inlineStr">
+        <is>
+          <t>力宠（已卖出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="29" t="inlineStr">
         <is>
           <t>召唤兽采购</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B49" s="29" t="inlineStr">
         <is>
           <t>购入法宠</t>
         </is>
       </c>
-      <c r="C41" s="8" t="n">
+      <c r="C49" s="30" t="n">
         <v>106</v>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D49" s="29" t="inlineStr">
         <is>
           <t>法宠（后续卖出）</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="16.5" customHeight="1">
-      <c r="A42" s="19" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="29" t="inlineStr">
         <is>
           <t>召唤兽采购</t>
         </is>
       </c>
-      <c r="B42" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79龙鲤 </t>
-        </is>
-      </c>
-      <c r="C42" s="20" t="n">
+      <c r="B50" s="29" t="inlineStr">
+        <is>
+          <t>79龙鲤</t>
+        </is>
+      </c>
+      <c r="C50" s="30" t="n">
         <v>68.25</v>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D50" s="29" t="inlineStr">
         <is>
           <t>力宠</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1">
-      <c r="A43" s="19" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="29" t="inlineStr">
         <is>
           <t>召唤兽采购</t>
         </is>
       </c>
-      <c r="B43" s="19" t="inlineStr">
+      <c r="B51" s="29" t="inlineStr">
         <is>
           <t>79龙鲤 2</t>
         </is>
       </c>
-      <c r="C43" s="20" t="n">
+      <c r="C51" s="30" t="n">
         <v>65</v>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D51" s="29" t="inlineStr">
         <is>
           <t>力宠</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="16.5" customHeight="1">
-      <c r="A44" s="19" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="29" t="inlineStr">
         <is>
           <t>召唤兽采购</t>
         </is>
       </c>
-      <c r="B44" s="19" t="inlineStr">
+      <c r="B52" s="29" t="inlineStr">
         <is>
           <t>须弥画魂高魔心带套0903</t>
         </is>
       </c>
-      <c r="C44" s="20" t="n">
+      <c r="C52" s="30" t="n">
         <v>409</v>
       </c>
-      <c r="D44" s="19" t="inlineStr">
+      <c r="D52" s="29" t="inlineStr">
         <is>
           <t>法宠</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="16.5" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="29" t="inlineStr">
         <is>
           <t>召唤兽采购</t>
         </is>
       </c>
-      <c r="B45" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">龙鲤0908 </t>
-        </is>
-      </c>
-      <c r="C45" s="20" t="n">
+      <c r="B53" s="29" t="inlineStr">
+        <is>
+          <t>龙鲤0908</t>
+        </is>
+      </c>
+      <c r="C53" s="30" t="n">
         <v>177</v>
       </c>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="D53" s="29" t="inlineStr">
         <is>
           <t>力宠</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1">
-      <c r="A46" s="19" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="29" t="inlineStr">
         <is>
           <t>召唤兽采购</t>
         </is>
       </c>
-      <c r="B46" s="19" t="inlineStr">
+      <c r="B54" s="29" t="inlineStr">
         <is>
           <t>三技能女娲0908</t>
         </is>
       </c>
-      <c r="C46" s="20" t="n">
+      <c r="C54" s="30" t="n">
         <v>160</v>
       </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="D54" s="29" t="inlineStr">
         <is>
           <t>力宠</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="19" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="29" t="inlineStr">
         <is>
           <t>召唤兽采购</t>
         </is>
       </c>
-      <c r="B47" s="19" t="inlineStr">
+      <c r="B55" s="29" t="inlineStr">
         <is>
           <t>雷鸟人须弥 9月20</t>
         </is>
       </c>
-      <c r="C47" s="20" t="n">
+      <c r="C55" s="30" t="n">
         <v>210</v>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D55" s="29" t="inlineStr">
         <is>
           <t>须弥法宠</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="26" customHeight="1">
-      <c r="A48" s="19" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="29" t="inlineStr">
         <is>
           <t>召唤兽采购</t>
         </is>
       </c>
-      <c r="B48" s="19" t="inlineStr">
+      <c r="B56" s="29" t="inlineStr">
         <is>
           <t>雷鸟人须弥 9月11</t>
         </is>
       </c>
-      <c r="C48" s="20" t="n">
+      <c r="C56" s="30" t="n">
         <v>240</v>
       </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="D56" s="29" t="inlineStr">
         <is>
           <t>须弥法宠</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1">
-      <c r="A49" s="21" t="inlineStr"/>
-      <c r="B49" s="21" t="inlineStr">
-        <is>
-          <t>购宠小计</t>
-        </is>
-      </c>
-      <c r="C49" s="22">
-        <f>SUM(C37:C48)</f>
+    <row r="57">
+      <c r="A57" s="31" t="n"/>
+      <c r="B57" s="31" t="n"/>
+      <c r="C57" s="32" t="n"/>
+      <c r="D57" s="31" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="31" t="n"/>
+      <c r="B58" s="31" t="n"/>
+      <c r="C58" s="32" t="n"/>
+      <c r="D58" s="31" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="31" t="n"/>
+      <c r="B59" s="31" t="n"/>
+      <c r="C59" s="32" t="n"/>
+      <c r="D59" s="31" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="31" t="n"/>
+      <c r="B60" s="31" t="n"/>
+      <c r="C60" s="32" t="n"/>
+      <c r="D60" s="31" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="31" t="n"/>
+      <c r="B61" s="31" t="n"/>
+      <c r="C61" s="32" t="n"/>
+      <c r="D61" s="31" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="33" t="n"/>
+      <c r="B62" s="33" t="inlineStr">
+        <is>
+          <t>召唤小计</t>
+        </is>
+      </c>
+      <c r="C62" s="34">
+        <f>SUM(C45:C61)</f>
         <v/>
       </c>
-      <c r="D49" s="21" t="inlineStr">
-        <is>
-          <t>宠物采购总花费</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="16.5" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="D62" s="33" t="n"/>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="27" t="inlineStr">
         <is>
           <t>▌装备采购</t>
         </is>
       </c>
-      <c r="B50" s="17" t="n"/>
-      <c r="C50" s="17" t="n"/>
-      <c r="D50" s="18" t="n"/>
-    </row>
-    <row r="51" ht="16.5" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="B64" s="37" t="n"/>
+      <c r="C64" s="37" t="n"/>
+      <c r="D64" s="38" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="29" t="inlineStr">
         <is>
           <t>装备采购</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B65" s="29" t="inlineStr">
         <is>
           <t>主号武器</t>
         </is>
       </c>
-      <c r="C51" s="8" t="n">
+      <c r="C65" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D65" s="29" t="inlineStr">
         <is>
           <t>主力角色装备</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="16.5" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
         <is>
           <t>装备采购</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B66" s="29" t="inlineStr">
         <is>
           <t>主号鞋子</t>
         </is>
       </c>
-      <c r="C52" s="8" t="n">
+      <c r="C66" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="D52" s="9" t="inlineStr">
+      <c r="D66" s="29" t="inlineStr">
         <is>
           <t>主力角色装备</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="16.5" customHeight="1">
-      <c r="A53" s="9" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
         <is>
           <t>装备采购</t>
         </is>
       </c>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="B67" s="29" t="inlineStr">
         <is>
           <t>4 角色 100 级国标武器</t>
         </is>
       </c>
-      <c r="C53" s="8" t="n">
+      <c r="C67" s="30" t="n">
         <v>40.5</v>
       </c>
-      <c r="D53" s="9" t="inlineStr">
+      <c r="D67" s="29" t="inlineStr">
         <is>
           <t>其余小号武器</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="16.5" customHeight="1">
-      <c r="A54" s="19" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>装备采购</t>
         </is>
       </c>
-      <c r="B54" s="19" t="inlineStr">
+      <c r="B68" s="29" t="inlineStr">
         <is>
           <t>后排灵饰109</t>
         </is>
       </c>
-      <c r="C54" s="20" t="n">
+      <c r="C68" s="30" t="n">
         <v>109</v>
       </c>
-      <c r="D54" s="19" t="inlineStr">
+      <c r="D68" s="29" t="inlineStr">
         <is>
           <t>装备采购</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="16.5" customHeight="1">
-      <c r="A55" s="19" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>装备采购</t>
         </is>
       </c>
-      <c r="B55" s="19" t="inlineStr">
+      <c r="B69" s="29" t="inlineStr">
         <is>
           <t>风伯套装48</t>
         </is>
       </c>
-      <c r="C55" s="20" t="n">
+      <c r="C69" s="30" t="n">
         <v>48</v>
       </c>
-      <c r="D55" s="19" t="inlineStr">
+      <c r="D69" s="29" t="inlineStr">
         <is>
           <t>装备采购</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="16.5" customHeight="1">
-      <c r="A56" s="19" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>装备采购</t>
         </is>
       </c>
-      <c r="B56" s="19" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>吸血鬼鞋子（套牢）</t>
         </is>
       </c>
-      <c r="C56" s="20" t="n">
+      <c r="C70" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="D56" s="19" t="inlineStr">
+      <c r="D70" s="29" t="inlineStr">
         <is>
           <t>装备采购</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="19" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>装备采购</t>
         </is>
       </c>
-      <c r="B57" s="19" t="inlineStr">
+      <c r="B71" s="29" t="inlineStr">
         <is>
           <t>国标武器</t>
         </is>
       </c>
-      <c r="C57" s="20" t="n">
+      <c r="C71" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="D57" s="19" t="inlineStr">
+      <c r="D71" s="29" t="inlineStr">
         <is>
           <t>装备采购</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="19" t="inlineStr">
-        <is>
-          <t>装备采购</t>
-        </is>
-      </c>
-      <c r="B58" s="19" t="n"/>
-      <c r="C58" s="20" t="n"/>
-      <c r="D58" s="19" t="n"/>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="21" t="inlineStr"/>
-      <c r="B59" s="21" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="31" t="n"/>
+      <c r="B72" s="31" t="n"/>
+      <c r="C72" s="32" t="n"/>
+      <c r="D72" s="31" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="n"/>
+      <c r="B73" s="31" t="n"/>
+      <c r="C73" s="32" t="n"/>
+      <c r="D73" s="31" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="n"/>
+      <c r="B74" s="31" t="n"/>
+      <c r="C74" s="32" t="n"/>
+      <c r="D74" s="31" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="n"/>
+      <c r="B75" s="31" t="n"/>
+      <c r="C75" s="32" t="n"/>
+      <c r="D75" s="31" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="n"/>
+      <c r="B76" s="31" t="n"/>
+      <c r="C76" s="32" t="n"/>
+      <c r="D76" s="31" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="33" t="n"/>
+      <c r="B77" s="33" t="inlineStr">
         <is>
           <t>装备小计</t>
         </is>
       </c>
-      <c r="C59" s="22">
-        <f>SUM(C51:C58)</f>
+      <c r="C77" s="34">
+        <f>SUM(C65:C76)</f>
         <v/>
       </c>
-      <c r="D59" s="21" t="inlineStr">
-        <is>
-          <t>装备总花费</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1"/>
-    <row r="61" ht="16.5" customHeight="1">
-      <c r="A61" s="24" t="n"/>
-      <c r="B61" s="24" t="inlineStr">
+      <c r="D77" s="33" t="n"/>
+    </row>
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" s="35" t="n"/>
+      <c r="B79" s="35" t="inlineStr">
         <is>
           <t>全部支出合计</t>
         </is>
       </c>
-      <c r="C61" s="11">
-        <f>C14+C35+C49+C59</f>
+      <c r="C79" s="36">
+        <f>C15+C42+C62+C77</f>
         <v/>
       </c>
-      <c r="D61" s="24" t="inlineStr">
-        <is>
-          <t>所有板块总支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16.5" customHeight="1"/>
-    <row r="63" ht="16.5" customHeight="1">
-      <c r="A63" s="14" t="inlineStr">
-        <is>
-          <t>📌 操作说明：在黄色底纹行录入新支出，金额填入 C 列，小计和合计自动更新。</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="14" t="inlineStr">
-        <is>
-          <t>📌 如需更多行：右键插入行 → 从上方黄色行复制格式即可。</t>
+      <c r="D79" s="35" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>📌 在黄色空行录入新支出，金额填 C 列，小计和合计自动更新</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="A44:D44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2349,7 +2512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2358,731 +2521,787 @@
     <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>梦幻西游 · 游戏变现收入明细表（黄色行为新增录入区）</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>收入分类</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>变现项目</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="26" t="inlineStr">
         <is>
           <t>金额 (元)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="26" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>▌宠物变现</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n"/>
-      <c r="C3" s="17" t="n"/>
-      <c r="D3" s="18" t="n"/>
-    </row>
-    <row r="4" ht="16.5" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="B3" s="37" t="n"/>
+      <c r="C3" s="37" t="n"/>
+      <c r="D3" s="38" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>宠物变现</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>出售法宠回款</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="30" t="n">
         <v>85.5</v>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>采购法宠卖出收入</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>宠物变现</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>龙鲤</t>
         </is>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="30" t="n">
         <v>161.5</v>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>卖出</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>宠物变现</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>吸血鬼</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="30" t="n">
         <v>123.5</v>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>卖出</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>宠物变现</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>3JN胚子</t>
         </is>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="30" t="n">
         <v>9.5</v>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>卖出</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>宠物变现</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>画魂  8月29</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="30" t="n">
         <v>115</v>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>卖出</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>宠物变现</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>3JN胚子  8月10</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="30" t="n">
         <v>9.5</v>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>卖出</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>宠物变现</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>龙鲤 胚子*2</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="30" t="n">
         <v>133</v>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>卖出</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>宠物变现</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>蝴蝶仙子*2</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="30" t="n">
         <v>66.5</v>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>卖出</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>宠物变现</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>地摊律法女娲  9月12</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="30" t="n">
         <v>14.5</v>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>卖出</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>宠物变现</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>地摊灵符女娲法  9月15</t>
         </is>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="30" t="n">
         <v>14.5</v>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>卖出</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>宠物变现</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>物品 80环装</t>
         </is>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="30" t="n">
         <v>9.5</v>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>卖出</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="21" t="inlineStr"/>
-      <c r="B15" s="21" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="31" t="n"/>
+      <c r="B15" s="31" t="n"/>
+      <c r="C15" s="32" t="n"/>
+      <c r="D15" s="31" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n"/>
+      <c r="B16" s="31" t="n"/>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="31" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n"/>
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="31" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n"/>
+      <c r="B18" s="31" t="n"/>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n"/>
+      <c r="B19" s="31" t="n"/>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="n"/>
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>宠物小计</t>
         </is>
       </c>
-      <c r="C15" s="22">
-        <f>SUM(C4:C14)</f>
+      <c r="C20" s="34">
+        <f>SUM(C4:C19)</f>
         <v/>
       </c>
-      <c r="D15" s="21" t="inlineStr"/>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="D20" s="33" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>▌物资变现</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="17" t="n"/>
-      <c r="D16" s="18" t="n"/>
-    </row>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="B22" s="37" t="n"/>
+      <c r="C22" s="37" t="n"/>
+      <c r="D22" s="38" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>第一坨菜售卖</t>
         </is>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C23" s="30" t="n">
         <v>202</v>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>游戏产出物资</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>小菜 1</t>
         </is>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C24" s="30" t="n">
         <v>67.45</v>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D24" s="29" t="inlineStr">
         <is>
           <t>新增变现</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>小菜 2</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C25" s="30" t="n">
         <v>67.45</v>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D25" s="29" t="inlineStr">
         <is>
           <t>新增变现</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>小菜 3</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C26" s="30" t="n">
         <v>66.78</v>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D26" s="29" t="inlineStr">
         <is>
           <t>新增变现</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t>小菜4</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C27" s="30" t="n">
         <v>66.78</v>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
         <is>
           <t>新增变现</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B28" s="29" t="inlineStr">
         <is>
           <t>小菜5</t>
         </is>
       </c>
-      <c r="C22" s="20" t="n">
+      <c r="C28" s="30" t="n">
         <v>66.02</v>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D28" s="29" t="inlineStr">
         <is>
           <t>新增变现</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>小菜6</t>
         </is>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C29" s="30" t="n">
         <v>65.55</v>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D29" s="29" t="inlineStr">
         <is>
           <t>新增变现</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B30" s="29" t="inlineStr">
         <is>
           <t>小菜7</t>
         </is>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C30" s="30" t="n">
         <v>66.02</v>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D30" s="29" t="inlineStr">
         <is>
           <t>新增变现</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B31" s="29" t="inlineStr">
         <is>
           <t>小菜8   8月29</t>
         </is>
       </c>
-      <c r="C25" s="20" t="n">
+      <c r="C31" s="30" t="n">
         <v>69.2</v>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D31" s="29" t="inlineStr">
         <is>
           <t>新增变现</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B32" s="29" t="inlineStr">
         <is>
           <t>小菜    8月11</t>
         </is>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C32" s="30" t="n">
         <v>68</v>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D32" s="29" t="inlineStr">
         <is>
           <t>新增变现</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B33" s="29" t="inlineStr">
         <is>
           <t>8月20</t>
         </is>
       </c>
-      <c r="C27" s="20" t="n">
+      <c r="C33" s="30" t="n">
         <v>41</v>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D33" s="29" t="inlineStr">
         <is>
           <t>新增变现</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B34" s="29" t="inlineStr">
         <is>
           <t>8月23</t>
         </is>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C34" s="30" t="n">
         <v>67.7</v>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D34" s="29" t="inlineStr">
         <is>
           <t>新增变现</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B35" s="29" t="inlineStr">
         <is>
           <t>8月13</t>
         </is>
       </c>
-      <c r="C29" s="20" t="n">
+      <c r="C35" s="30" t="n">
         <v>68</v>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D35" s="29" t="inlineStr">
         <is>
           <t>新增变现</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr">
+      <c r="B36" s="29" t="inlineStr">
         <is>
           <t>小菜9 8月27</t>
         </is>
       </c>
-      <c r="C30" s="20" t="n">
+      <c r="C36" s="30" t="n">
         <v>41.82</v>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D36" s="29" t="inlineStr">
         <is>
           <t>新增变现</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B31" s="19" t="inlineStr">
+      <c r="B37" s="29" t="inlineStr">
         <is>
           <t>出菜1坨 9月11</t>
         </is>
       </c>
-      <c r="C31" s="20" t="n">
+      <c r="C37" s="30" t="n">
         <v>197</v>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D37" s="29" t="inlineStr">
         <is>
           <t>新增变现</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B32" s="19" t="inlineStr">
+      <c r="B38" s="29" t="inlineStr">
         <is>
           <t>出菜400W 9月17</t>
         </is>
       </c>
-      <c r="C32" s="20" t="n">
+      <c r="C38" s="30" t="n">
         <v>25.84</v>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D38" s="29" t="inlineStr">
         <is>
           <t>新增变现</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B33" s="19" t="inlineStr">
+      <c r="B39" s="29" t="inlineStr">
         <is>
           <t>出菜3000W 9月17</t>
         </is>
       </c>
-      <c r="C33" s="20" t="n">
+      <c r="C39" s="30" t="n">
         <v>191.9</v>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D39" s="29" t="inlineStr">
         <is>
           <t>新增变现</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1">
-      <c r="A34" s="19" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B34" s="19" t="inlineStr">
+      <c r="B40" s="29" t="inlineStr">
         <is>
           <t>出菜半坨 9月11</t>
         </is>
       </c>
-      <c r="C34" s="20" t="n">
+      <c r="C40" s="30" t="n">
         <v>111</v>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D40" s="29" t="inlineStr">
         <is>
           <t>新增变现</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B35" s="19" t="inlineStr">
+      <c r="B41" s="29" t="inlineStr">
         <is>
           <t>出一坨小菜 9月21</t>
         </is>
       </c>
-      <c r="C35" s="19" t="n">
+      <c r="C41" s="30" t="n">
         <v>65</v>
       </c>
-      <c r="D35" s="19" t="inlineStr">
+      <c r="D41" s="29" t="inlineStr">
         <is>
           <t>新增变现</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="29" t="inlineStr">
         <is>
           <t>物资变现</t>
         </is>
       </c>
-      <c r="B36" s="19" t="inlineStr">
+      <c r="B42" s="29" t="inlineStr">
         <is>
           <t>卖古代瑞兽胚子 9月23</t>
         </is>
       </c>
-      <c r="C36" s="19" t="n">
+      <c r="C42" s="30" t="n">
         <v>9.5</v>
       </c>
-      <c r="D36" s="19" t="n"/>
-    </row>
-    <row r="37" ht="16.5" customHeight="1">
-      <c r="A37" s="23" t="n"/>
-      <c r="B37" s="23" t="inlineStr">
+      <c r="D42" s="29" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="31" t="n"/>
+      <c r="B43" s="31" t="n"/>
+      <c r="C43" s="32" t="n"/>
+      <c r="D43" s="31" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="31" t="n"/>
+      <c r="B44" s="31" t="n"/>
+      <c r="C44" s="32" t="n"/>
+      <c r="D44" s="31" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="n"/>
+      <c r="B45" s="31" t="n"/>
+      <c r="C45" s="32" t="n"/>
+      <c r="D45" s="31" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="31" t="n"/>
+      <c r="B46" s="31" t="n"/>
+      <c r="C46" s="32" t="n"/>
+      <c r="D46" s="31" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="31" t="n"/>
+      <c r="B47" s="31" t="n"/>
+      <c r="C47" s="32" t="n"/>
+      <c r="D47" s="31" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="33" t="n"/>
+      <c r="B48" s="33" t="inlineStr">
         <is>
           <t>物资小计</t>
         </is>
       </c>
-      <c r="C37" s="23">
-        <f>SUM(C17:C36)</f>
+      <c r="C48" s="34">
+        <f>SUM(C23:C47)</f>
         <v/>
       </c>
-      <c r="D37" s="23" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr"/>
-      <c r="B38" s="21" t="n"/>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>所有回款合计</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16.5" customHeight="1">
-      <c r="B39" t="inlineStr">
+      <c r="D48" s="33" t="n"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="35" t="n"/>
+      <c r="B50" s="35" t="inlineStr">
         <is>
           <t>全部变现总收入</t>
         </is>
       </c>
-      <c r="C39">
-        <f>C15+C37</f>
+      <c r="C50" s="36">
+        <f>C20+C48</f>
         <v/>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>📌 操作说明：在黄色底纹行录入新收入，金额填入 C 列，小计和合计自动更新。</t>
+      <c r="D50" s="35" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>📌 在黄色空行录入新收入，金额填 C 列，小计和合计自动更新</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A22:D22"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A40:D40"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A52:D52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3133,7 +3352,7 @@
         </is>
       </c>
       <c r="B3" s="5">
-        <f>支出明细表!C61</f>
+        <f>支出明细表!C79</f>
         <v/>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -3149,7 +3368,7 @@
         </is>
       </c>
       <c r="B4" s="8">
-        <f>游戏变现收入明细表!C39</f>
+        <f>游戏变现收入明细表!C50</f>
         <v/>
       </c>
       <c r="C4" s="9" t="inlineStr">

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -2781,10 +2781,24 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="n"/>
-      <c r="B15" s="31" t="n"/>
-      <c r="C15" s="32" t="n"/>
-      <c r="D15" s="31" t="n"/>
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>宠物变现</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>卖古代瑞兽胚子 9月23</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="31" t="n"/>
@@ -2811,47 +2825,34 @@
       <c r="D19" s="31" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="33" t="n"/>
-      <c r="B20" s="33" t="inlineStr">
+      <c r="A20" s="31" t="n"/>
+      <c r="B20" s="31" t="n"/>
+      <c r="C20" s="32" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="n"/>
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>宠物小计</t>
         </is>
       </c>
-      <c r="C20" s="34">
-        <f>SUM(C4:C19)</f>
+      <c r="C21" s="34">
+        <f>SUM(C4:C20)</f>
         <v/>
       </c>
-      <c r="D20" s="33" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="D21" s="33" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1"/>
+    <row r="23">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>▌物资变现</t>
         </is>
       </c>
-      <c r="B22" s="37" t="n"/>
-      <c r="C22" s="37" t="n"/>
-      <c r="D22" s="38" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="29" t="inlineStr">
-        <is>
-          <t>物资变现</t>
-        </is>
-      </c>
-      <c r="B23" s="29" t="inlineStr">
-        <is>
-          <t>第一坨菜售卖</t>
-        </is>
-      </c>
-      <c r="C23" s="30" t="n">
-        <v>202</v>
-      </c>
-      <c r="D23" s="29" t="inlineStr">
-        <is>
-          <t>游戏产出物资</t>
-        </is>
-      </c>
+      <c r="B23" s="37" t="n"/>
+      <c r="C23" s="37" t="n"/>
+      <c r="D23" s="38" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="29" t="inlineStr">
@@ -2861,15 +2862,15 @@
       </c>
       <c r="B24" s="29" t="inlineStr">
         <is>
-          <t>小菜 1</t>
+          <t>第一坨菜售卖</t>
         </is>
       </c>
       <c r="C24" s="30" t="n">
-        <v>67.45</v>
+        <v>202</v>
       </c>
       <c r="D24" s="29" t="inlineStr">
         <is>
-          <t>新增变现</t>
+          <t>游戏产出物资</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2882,7 @@
       </c>
       <c r="B25" s="29" t="inlineStr">
         <is>
-          <t>小菜 2</t>
+          <t>小菜 1</t>
         </is>
       </c>
       <c r="C25" s="30" t="n">
@@ -2901,11 +2902,11 @@
       </c>
       <c r="B26" s="29" t="inlineStr">
         <is>
-          <t>小菜 3</t>
+          <t>小菜 2</t>
         </is>
       </c>
       <c r="C26" s="30" t="n">
-        <v>66.78</v>
+        <v>67.45</v>
       </c>
       <c r="D26" s="29" t="inlineStr">
         <is>
@@ -2921,7 +2922,7 @@
       </c>
       <c r="B27" s="29" t="inlineStr">
         <is>
-          <t>小菜4</t>
+          <t>小菜 3</t>
         </is>
       </c>
       <c r="C27" s="30" t="n">
@@ -2941,11 +2942,11 @@
       </c>
       <c r="B28" s="29" t="inlineStr">
         <is>
-          <t>小菜5</t>
+          <t>小菜4</t>
         </is>
       </c>
       <c r="C28" s="30" t="n">
-        <v>66.02</v>
+        <v>66.78</v>
       </c>
       <c r="D28" s="29" t="inlineStr">
         <is>
@@ -2961,11 +2962,11 @@
       </c>
       <c r="B29" s="29" t="inlineStr">
         <is>
-          <t>小菜6</t>
+          <t>小菜5</t>
         </is>
       </c>
       <c r="C29" s="30" t="n">
-        <v>65.55</v>
+        <v>66.02</v>
       </c>
       <c r="D29" s="29" t="inlineStr">
         <is>
@@ -2981,11 +2982,11 @@
       </c>
       <c r="B30" s="29" t="inlineStr">
         <is>
-          <t>小菜7</t>
+          <t>小菜6</t>
         </is>
       </c>
       <c r="C30" s="30" t="n">
-        <v>66.02</v>
+        <v>65.55</v>
       </c>
       <c r="D30" s="29" t="inlineStr">
         <is>
@@ -3001,11 +3002,11 @@
       </c>
       <c r="B31" s="29" t="inlineStr">
         <is>
-          <t>小菜8   8月29</t>
+          <t>小菜7</t>
         </is>
       </c>
       <c r="C31" s="30" t="n">
-        <v>69.2</v>
+        <v>66.02</v>
       </c>
       <c r="D31" s="29" t="inlineStr">
         <is>
@@ -3021,11 +3022,11 @@
       </c>
       <c r="B32" s="29" t="inlineStr">
         <is>
-          <t>小菜    8月11</t>
+          <t>小菜8   8月29</t>
         </is>
       </c>
       <c r="C32" s="30" t="n">
-        <v>68</v>
+        <v>69.2</v>
       </c>
       <c r="D32" s="29" t="inlineStr">
         <is>
@@ -3041,11 +3042,11 @@
       </c>
       <c r="B33" s="29" t="inlineStr">
         <is>
-          <t>8月20</t>
+          <t>小菜    8月11</t>
         </is>
       </c>
       <c r="C33" s="30" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="D33" s="29" t="inlineStr">
         <is>
@@ -3061,11 +3062,11 @@
       </c>
       <c r="B34" s="29" t="inlineStr">
         <is>
-          <t>8月23</t>
+          <t>8月20</t>
         </is>
       </c>
       <c r="C34" s="30" t="n">
-        <v>67.7</v>
+        <v>41</v>
       </c>
       <c r="D34" s="29" t="inlineStr">
         <is>
@@ -3081,11 +3082,11 @@
       </c>
       <c r="B35" s="29" t="inlineStr">
         <is>
-          <t>8月13</t>
+          <t>8月23</t>
         </is>
       </c>
       <c r="C35" s="30" t="n">
-        <v>68</v>
+        <v>67.7</v>
       </c>
       <c r="D35" s="29" t="inlineStr">
         <is>
@@ -3101,11 +3102,11 @@
       </c>
       <c r="B36" s="29" t="inlineStr">
         <is>
-          <t>小菜9 8月27</t>
+          <t>8月13</t>
         </is>
       </c>
       <c r="C36" s="30" t="n">
-        <v>41.82</v>
+        <v>68</v>
       </c>
       <c r="D36" s="29" t="inlineStr">
         <is>
@@ -3121,11 +3122,11 @@
       </c>
       <c r="B37" s="29" t="inlineStr">
         <is>
-          <t>出菜1坨 9月11</t>
+          <t>小菜9 8月27</t>
         </is>
       </c>
       <c r="C37" s="30" t="n">
-        <v>197</v>
+        <v>41.82</v>
       </c>
       <c r="D37" s="29" t="inlineStr">
         <is>
@@ -3141,11 +3142,11 @@
       </c>
       <c r="B38" s="29" t="inlineStr">
         <is>
-          <t>出菜400W 9月17</t>
+          <t>出菜1坨 9月11</t>
         </is>
       </c>
       <c r="C38" s="30" t="n">
-        <v>25.84</v>
+        <v>197</v>
       </c>
       <c r="D38" s="29" t="inlineStr">
         <is>
@@ -3161,11 +3162,11 @@
       </c>
       <c r="B39" s="29" t="inlineStr">
         <is>
-          <t>出菜3000W 9月17</t>
+          <t>出菜400W 9月17</t>
         </is>
       </c>
       <c r="C39" s="30" t="n">
-        <v>191.9</v>
+        <v>25.84</v>
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
@@ -3181,11 +3182,11 @@
       </c>
       <c r="B40" s="29" t="inlineStr">
         <is>
-          <t>出菜半坨 9月11</t>
+          <t>出菜3000W 9月17</t>
         </is>
       </c>
       <c r="C40" s="30" t="n">
-        <v>111</v>
+        <v>191.9</v>
       </c>
       <c r="D40" s="29" t="inlineStr">
         <is>
@@ -3201,11 +3202,11 @@
       </c>
       <c r="B41" s="29" t="inlineStr">
         <is>
-          <t>出一坨小菜 9月21</t>
+          <t>出菜半坨 9月11</t>
         </is>
       </c>
       <c r="C41" s="30" t="n">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="D41" s="29" t="inlineStr">
         <is>
@@ -3221,15 +3222,15 @@
       </c>
       <c r="B42" s="29" t="inlineStr">
         <is>
-          <t>卖古代瑞兽胚子 9月23</t>
+          <t>出一坨小菜 9月21</t>
         </is>
       </c>
       <c r="C42" s="30" t="n">
-        <v>9.5</v>
+        <v>65</v>
       </c>
       <c r="D42" s="29" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>新增变现</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3272,7 @@
         </is>
       </c>
       <c r="C48" s="34">
-        <f>SUM(C23:C47)</f>
+        <f>SUM(C24:C47)</f>
         <v/>
       </c>
       <c r="D48" s="33" t="n"/>
@@ -3284,7 +3285,7 @@
         </is>
       </c>
       <c r="C50" s="36">
-        <f>C20+C48</f>
+        <f>C21+C48</f>
         <v/>
       </c>
       <c r="D50" s="35" t="n"/>

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -3235,10 +3235,24 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="31" t="n"/>
-      <c r="B43" s="31" t="n"/>
-      <c r="C43" s="32" t="n"/>
-      <c r="D43" s="31" t="n"/>
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>物资变现</t>
+        </is>
+      </c>
+      <c r="B43" s="29" t="inlineStr">
+        <is>
+          <t>小菜 0924</t>
+        </is>
+      </c>
+      <c r="C43" s="30" t="n">
+        <v>65</v>
+      </c>
+      <c r="D43" s="29" t="inlineStr">
+        <is>
+          <t>新增变现</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="31" t="n"/>

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="177">
   <si>
     <t>梦幻西游 · 支出明细表（当前新号账期｜黄色行为新增录入区）</t>
   </si>
@@ -125,6 +125,12 @@
   </si>
   <si>
     <t>▌宠物变现</t>
+  </si>
+  <si>
+    <t>涂山T</t>
+  </si>
+  <si>
+    <t>9月29</t>
   </si>
   <si>
     <t>宠物变现 小计</t>
@@ -1950,9 +1956,15 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
+      <c r="A4" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="19">
+        <v>12.25</v>
+      </c>
       <c r="D4" s="19"/>
     </row>
     <row r="5" spans="1:4">
@@ -1999,16 +2011,16 @@
     </row>
     <row r="12" ht="16.5" spans="1:4">
       <c r="B12" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" s="12">
         <f>SUM(C4:C11)</f>
-        <v>0</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="14" ht="15" spans="1:4">
       <c r="A14" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -2016,20 +2028,26 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C15" s="19">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="D15" s="19"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
+      <c r="A16" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="19">
+        <v>27</v>
+      </c>
       <c r="D16" s="19"/>
     </row>
     <row r="17" spans="1:4">
@@ -2070,16 +2088,16 @@
     </row>
     <row r="23" ht="16.5" spans="1:4">
       <c r="B23" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C23" s="12">
         <f>SUM(C15:C22)</f>
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" ht="15" spans="1:4">
       <c r="A25" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -2147,7 +2165,7 @@
     </row>
     <row r="36" ht="16.5" spans="1:4">
       <c r="B36" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C36" s="12">
         <f>SUM(C26:C35)</f>
@@ -2156,16 +2174,16 @@
     </row>
     <row r="38" ht="15" spans="1:4">
       <c r="B38" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C38" s="16">
         <f>C12+C23+C36</f>
-        <v>125</v>
+        <v>142.25</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2191,95 +2209,95 @@
   <sheetData>
     <row r="1" ht="21" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" ht="15" spans="1:3">
       <c r="A2" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B3" s="10">
         <f>支出明细表!C32</f>
         <v>13320</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" s="10">
         <f>游戏变现收入明细表!C38</f>
-        <v>125</v>
+        <v>142.25</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" ht="15" spans="1:3">
       <c r="A5" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B5" s="16">
         <f>B3-B4</f>
-        <v>13195</v>
+        <v>13177.75</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" ht="15" spans="1:3">
       <c r="A7" s="18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B8" s="5">
         <v>4000.69</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" ht="15" spans="1:3">
       <c r="A10" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -2306,55 +2324,55 @@
   <sheetData>
     <row r="1" ht="21" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" ht="15" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B5" s="5">
         <v>6455.7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B6" s="5">
         <v>2455.01</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B7" s="5">
         <v>4000.69</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" ht="15" spans="1:4">
@@ -2384,13 +2402,13 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C12" s="10">
         <v>391.9</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2398,13 +2416,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C13" s="10">
         <v>400</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2412,13 +2430,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C14" s="10">
         <v>519</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2426,13 +2444,13 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C15" s="10">
         <v>500</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2440,13 +2458,13 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C16" s="10">
         <v>866</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2454,13 +2472,13 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C17" s="10">
         <v>460</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -2485,13 +2503,13 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C21" s="10">
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2499,13 +2517,13 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C22" s="10">
         <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2513,13 +2531,13 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C23" s="10">
         <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2527,13 +2545,13 @@
         <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C24" s="10">
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2541,13 +2559,13 @@
         <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C25" s="10">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2555,13 +2573,13 @@
         <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C26" s="10">
         <v>10</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2569,13 +2587,13 @@
         <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C27" s="10">
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2583,13 +2601,13 @@
         <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C28" s="10">
         <v>300</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2597,13 +2615,13 @@
         <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C29" s="10">
         <v>125</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2611,13 +2629,13 @@
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C30" s="10">
         <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2625,13 +2643,13 @@
         <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C31" s="10">
         <v>1.05</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2639,13 +2657,13 @@
         <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C32" s="10">
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2653,13 +2671,13 @@
         <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C33" s="10">
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2667,13 +2685,13 @@
         <v>15</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C34" s="10">
         <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2681,13 +2699,13 @@
         <v>15</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C35" s="10">
         <v>290</v>
       </c>
       <c r="D35" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2695,13 +2713,13 @@
         <v>15</v>
       </c>
       <c r="B36" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C36" s="10">
         <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2709,13 +2727,13 @@
         <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C37" s="10">
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2723,13 +2741,13 @@
         <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C38" s="10">
         <v>20</v>
       </c>
       <c r="D38" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2737,13 +2755,13 @@
         <v>15</v>
       </c>
       <c r="B39" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C39" s="10">
         <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2751,13 +2769,13 @@
         <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C40" s="10">
         <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:4">
@@ -2779,170 +2797,170 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B44" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C44" s="10">
         <v>128</v>
       </c>
       <c r="D44" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C45" s="10">
         <v>140</v>
       </c>
       <c r="D45" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B46" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C46" s="10">
         <v>120</v>
       </c>
       <c r="D46" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B47" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C47" s="10">
         <v>168</v>
       </c>
       <c r="D47" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B48" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C48" s="10">
         <v>106</v>
       </c>
       <c r="D48" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B49" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C49" s="10">
         <v>68.25</v>
       </c>
       <c r="D49" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B50" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C50" s="10">
         <v>65</v>
       </c>
       <c r="D50" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B51" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C51" s="10">
         <v>409</v>
       </c>
       <c r="D51" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B52" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C52" s="10">
         <v>177</v>
       </c>
       <c r="D52" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B53" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C53" s="10">
         <v>160</v>
       </c>
       <c r="D53" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B54" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C54" s="10">
         <v>210</v>
       </c>
       <c r="D54" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B55" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C55" s="10">
         <v>240</v>
       </c>
       <c r="D55" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="1:4">
@@ -2964,100 +2982,100 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B59" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C59" s="10">
         <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B60" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C60" s="10">
         <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B61" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C61" s="10">
         <v>40.5</v>
       </c>
       <c r="D61" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B62" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C62" s="10">
         <v>109</v>
       </c>
       <c r="D62" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B63" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C63" s="10">
         <v>48</v>
       </c>
       <c r="D63" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C64" s="10">
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B65" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C65" s="10">
         <v>10</v>
       </c>
       <c r="D65" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:4">
@@ -3071,7 +3089,7 @@
     </row>
     <row r="68" ht="15" spans="1:4">
       <c r="B68" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C68" s="13">
         <f>C18+C41+C56+C66</f>
@@ -3080,7 +3098,7 @@
     </row>
     <row r="70" ht="18" spans="1:4">
       <c r="A70" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="71" ht="15" spans="1:4">
@@ -3107,203 +3125,203 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B73" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C73" s="10">
         <v>85.5</v>
       </c>
       <c r="D73" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B74" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C74" s="10">
         <v>161.5</v>
       </c>
       <c r="D74" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B75" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C75" s="10">
         <v>123.5</v>
       </c>
       <c r="D75" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B76" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C76" s="10">
         <v>9.5</v>
       </c>
       <c r="D76" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B77" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C77" s="10">
         <v>115</v>
       </c>
       <c r="D77" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B78" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C78" s="10">
         <v>9.5</v>
       </c>
       <c r="D78" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B79" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C79" s="10">
         <v>133</v>
       </c>
       <c r="D79" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B80" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C80" s="10">
         <v>66.5</v>
       </c>
       <c r="D80" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B81" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C81" s="10">
         <v>14.5</v>
       </c>
       <c r="D81" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B82" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C82" s="10">
         <v>14.5</v>
       </c>
       <c r="D82" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B83" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C83" s="10">
         <v>9.5</v>
       </c>
       <c r="D83" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B84" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C84" s="10">
         <v>9.5</v>
       </c>
       <c r="D84" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B85" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C85" s="10">
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B86" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C86" s="10">
         <v>9.5</v>
       </c>
       <c r="D86" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="87" ht="16.5" spans="1:4">
       <c r="B87" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C87" s="12">
         <f>SUM(C73:C86)</f>
@@ -3312,7 +3330,7 @@
     </row>
     <row r="89" ht="15" spans="1:4">
       <c r="A89" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B89" s="9"/>
       <c r="C89" s="9"/>
@@ -3320,287 +3338,287 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B90" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C90" s="10">
         <v>202</v>
       </c>
       <c r="D90" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B91" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C91" s="10">
         <v>67.45</v>
       </c>
       <c r="D91" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B92" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C92" s="10">
         <v>67.45</v>
       </c>
       <c r="D92" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B93" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C93" s="10">
         <v>66.78</v>
       </c>
       <c r="D93" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B94" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C94" s="10">
         <v>66.78</v>
       </c>
       <c r="D94" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B95" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C95" s="10">
         <v>66.02</v>
       </c>
       <c r="D95" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B96" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C96" s="10">
         <v>65.55</v>
       </c>
       <c r="D96" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B97" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C97" s="10">
         <v>66.02</v>
       </c>
       <c r="D97" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B98" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C98" s="10">
         <v>69.2</v>
       </c>
       <c r="D98" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B99" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C99" s="10">
         <v>68</v>
       </c>
       <c r="D99" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B100" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C100" s="10">
         <v>41</v>
       </c>
       <c r="D100" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B101" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C101" s="10">
         <v>67.7</v>
       </c>
       <c r="D101" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B102" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C102" s="10">
         <v>68</v>
       </c>
       <c r="D102" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B103" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C103" s="10">
         <v>41.82</v>
       </c>
       <c r="D103" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B104" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C104" s="10">
         <v>197</v>
       </c>
       <c r="D104" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B105" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C105" s="10">
         <v>25.84</v>
       </c>
       <c r="D105" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B106" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C106" s="10">
         <v>191.9</v>
       </c>
       <c r="D106" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B107" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C107" s="10">
         <v>111</v>
       </c>
       <c r="D107" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B108" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C108" s="10">
         <v>65</v>
       </c>
       <c r="D108" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B109" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C109" s="10">
         <v>65</v>
       </c>
       <c r="D109" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="110" ht="16.5" spans="1:4">
       <c r="B110" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C110" s="12">
         <f>SUM(C90:C109)</f>
@@ -3609,7 +3627,7 @@
     </row>
     <row r="112" ht="15" spans="1:4">
       <c r="B112" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C112" s="13">
         <f>C87+C110</f>
@@ -3618,7 +3636,7 @@
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\MHXY\chenlong5469-ui.github.io\now\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\MHH\now\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17775" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="支出明细表" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="187">
   <si>
     <t>梦幻西游 · 支出明细表（当前新号账期｜黄色行为新增录入区）</t>
   </si>
@@ -179,6 +179,9 @@
   </si>
   <si>
     <t>10月9号结算 （卖出女儿村440,垃圾画魂403</t>
+  </si>
+  <si>
+    <t>10月10号结算(247雷鸟人须弥</t>
   </si>
   <si>
     <t>旧号回笼 小计</t>
@@ -2201,9 +2204,15 @@
       <c r="D28" s="19"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
+      <c r="A29" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="19">
+        <v>247</v>
+      </c>
       <c r="D29" s="19"/>
     </row>
     <row r="30" spans="1:4">
@@ -2244,11 +2253,11 @@
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="1:4">
       <c r="B36" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C36" s="12">
         <f>SUM(C26:C35)</f>
-        <v>3006</v>
+        <v>3253</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:4">
@@ -2256,16 +2265,16 @@
         <v>44</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C38" s="16">
         <f>C12+C23+C36</f>
-        <v>3547.25</v>
+        <v>3794.25</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -2291,104 +2300,104 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:3">
       <c r="A2" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B3" s="10">
         <f>支出明细表!C33</f>
         <v>13470</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B4" s="10">
         <f>游戏变现收入明细表!C38</f>
-        <v>3547.25</v>
+        <v>3794.25</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:3">
       <c r="A5" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B5" s="16">
         <f>B3-B4</f>
-        <v>9922.75</v>
+        <v>9675.75</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:3">
       <c r="A7" s="18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B8" s="5">
         <v>4000.69</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B9" s="10">
         <f>B3+B8-B4</f>
-        <v>13923.44</v>
+        <v>13676.44</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:3">
       <c r="A10" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -2415,55 +2424,55 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B5" s="5">
         <v>6455.7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B6" s="5">
         <v>2455.01</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" s="5">
         <v>4000.69</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:4">
@@ -2493,13 +2502,13 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" s="10">
         <v>391.9</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2507,13 +2516,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" s="10">
         <v>400</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2521,13 +2530,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" s="10">
         <v>519</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2535,13 +2544,13 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C15" s="10">
         <v>500</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2549,13 +2558,13 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C16" s="10">
         <v>866</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2563,13 +2572,13 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C17" s="10">
         <v>460</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:4">
@@ -2594,13 +2603,13 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C21" s="10">
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2608,13 +2617,13 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C22" s="10">
         <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2622,13 +2631,13 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C23" s="10">
         <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2636,13 +2645,13 @@
         <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C24" s="10">
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2650,13 +2659,13 @@
         <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C25" s="10">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2664,13 +2673,13 @@
         <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C26" s="10">
         <v>10</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2678,13 +2687,13 @@
         <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C27" s="10">
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2692,13 +2701,13 @@
         <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C28" s="10">
         <v>300</v>
       </c>
       <c r="D28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2706,13 +2715,13 @@
         <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C29" s="10">
         <v>125</v>
       </c>
       <c r="D29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2720,13 +2729,13 @@
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C30" s="10">
         <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2734,13 +2743,13 @@
         <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C31" s="10">
         <v>1.05</v>
       </c>
       <c r="D31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2748,13 +2757,13 @@
         <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C32" s="10">
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2762,13 +2771,13 @@
         <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C33" s="10">
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2776,13 +2785,13 @@
         <v>15</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C34" s="10">
         <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2790,13 +2799,13 @@
         <v>15</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C35" s="10">
         <v>290</v>
       </c>
       <c r="D35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2804,13 +2813,13 @@
         <v>15</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C36" s="10">
         <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2818,13 +2827,13 @@
         <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C37" s="10">
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2832,13 +2841,13 @@
         <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C38" s="10">
         <v>20</v>
       </c>
       <c r="D38" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2846,13 +2855,13 @@
         <v>15</v>
       </c>
       <c r="B39" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C39" s="10">
         <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2860,13 +2869,13 @@
         <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C40" s="10">
         <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:4">
@@ -2888,170 +2897,170 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B44" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C44" s="10">
         <v>128</v>
       </c>
       <c r="D44" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B45" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C45" s="10">
         <v>140</v>
       </c>
       <c r="D45" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B46" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C46" s="10">
         <v>120</v>
       </c>
       <c r="D46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B47" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C47" s="10">
         <v>168</v>
       </c>
       <c r="D47" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C48" s="10">
         <v>106</v>
       </c>
       <c r="D48" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B49" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C49" s="10">
         <v>68.25</v>
       </c>
       <c r="D49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B50" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C50" s="10">
         <v>65</v>
       </c>
       <c r="D50" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B51" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C51" s="10">
         <v>409</v>
       </c>
       <c r="D51" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B52" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C52" s="10">
         <v>177</v>
       </c>
       <c r="D52" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B53" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C53" s="10">
         <v>160</v>
       </c>
       <c r="D53" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B54" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C54" s="10">
         <v>210</v>
       </c>
       <c r="D54" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B55" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C55" s="10">
         <v>240</v>
       </c>
       <c r="D55" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" ht="16.5" customHeight="1" spans="1:4">
@@ -3076,13 +3085,13 @@
         <v>24</v>
       </c>
       <c r="B59" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C59" s="10">
         <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3090,13 +3099,13 @@
         <v>24</v>
       </c>
       <c r="B60" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C60" s="10">
         <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3104,13 +3113,13 @@
         <v>24</v>
       </c>
       <c r="B61" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C61" s="10">
         <v>40.5</v>
       </c>
       <c r="D61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3118,13 +3127,13 @@
         <v>24</v>
       </c>
       <c r="B62" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C62" s="10">
         <v>109</v>
       </c>
       <c r="D62" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3132,13 +3141,13 @@
         <v>24</v>
       </c>
       <c r="B63" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C63" s="10">
         <v>48</v>
       </c>
       <c r="D63" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3146,13 +3155,13 @@
         <v>24</v>
       </c>
       <c r="B64" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C64" s="10">
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3160,13 +3169,13 @@
         <v>24</v>
       </c>
       <c r="B65" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C65" s="10">
         <v>10</v>
       </c>
       <c r="D65" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" ht="16.5" customHeight="1" spans="1:4">
@@ -3180,7 +3189,7 @@
     </row>
     <row r="68" ht="15" customHeight="1" spans="1:4">
       <c r="B68" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C68" s="13">
         <f>C18+C41+C56+C66</f>
@@ -3189,7 +3198,7 @@
     </row>
     <row r="70" ht="18" customHeight="1" spans="1:4">
       <c r="A70" s="14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:4">
@@ -3216,198 +3225,198 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B73" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C73" s="10">
         <v>85.5</v>
       </c>
       <c r="D73" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B74" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C74" s="10">
         <v>161.5</v>
       </c>
       <c r="D74" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B75" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C75" s="10">
         <v>123.5</v>
       </c>
       <c r="D75" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B76" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C76" s="10">
         <v>9.5</v>
       </c>
       <c r="D76" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B77" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C77" s="10">
         <v>115</v>
       </c>
       <c r="D77" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B78" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C78" s="10">
         <v>9.5</v>
       </c>
       <c r="D78" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B79" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C79" s="10">
         <v>133</v>
       </c>
       <c r="D79" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B80" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C80" s="10">
         <v>66.5</v>
       </c>
       <c r="D80" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B81" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C81" s="10">
         <v>14.5</v>
       </c>
       <c r="D81" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B82" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C82" s="10">
         <v>14.5</v>
       </c>
       <c r="D82" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B83" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C83" s="10">
         <v>9.5</v>
       </c>
       <c r="D83" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B84" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C84" s="10">
         <v>9.5</v>
       </c>
       <c r="D84" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B85" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C85" s="10">
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B86" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C86" s="10">
         <v>9.5</v>
       </c>
       <c r="D86" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="87" ht="16.5" customHeight="1" spans="1:4">
@@ -3432,13 +3441,13 @@
         <v>35</v>
       </c>
       <c r="B90" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C90" s="10">
         <v>202</v>
       </c>
       <c r="D90" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3446,13 +3455,13 @@
         <v>35</v>
       </c>
       <c r="B91" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C91" s="10">
         <v>67.45</v>
       </c>
       <c r="D91" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3460,13 +3469,13 @@
         <v>35</v>
       </c>
       <c r="B92" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C92" s="10">
         <v>67.45</v>
       </c>
       <c r="D92" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3474,13 +3483,13 @@
         <v>35</v>
       </c>
       <c r="B93" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C93" s="10">
         <v>66.78</v>
       </c>
       <c r="D93" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3488,13 +3497,13 @@
         <v>35</v>
       </c>
       <c r="B94" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C94" s="10">
         <v>66.78</v>
       </c>
       <c r="D94" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3502,13 +3511,13 @@
         <v>35</v>
       </c>
       <c r="B95" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C95" s="10">
         <v>66.02</v>
       </c>
       <c r="D95" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3516,13 +3525,13 @@
         <v>35</v>
       </c>
       <c r="B96" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C96" s="10">
         <v>65.55</v>
       </c>
       <c r="D96" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3530,13 +3539,13 @@
         <v>35</v>
       </c>
       <c r="B97" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C97" s="10">
         <v>66.02</v>
       </c>
       <c r="D97" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3544,13 +3553,13 @@
         <v>35</v>
       </c>
       <c r="B98" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C98" s="10">
         <v>69.2</v>
       </c>
       <c r="D98" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3558,13 +3567,13 @@
         <v>35</v>
       </c>
       <c r="B99" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C99" s="10">
         <v>68</v>
       </c>
       <c r="D99" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3572,13 +3581,13 @@
         <v>35</v>
       </c>
       <c r="B100" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C100" s="10">
         <v>41</v>
       </c>
       <c r="D100" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3586,13 +3595,13 @@
         <v>35</v>
       </c>
       <c r="B101" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C101" s="10">
         <v>67.7</v>
       </c>
       <c r="D101" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3600,13 +3609,13 @@
         <v>35</v>
       </c>
       <c r="B102" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C102" s="10">
         <v>68</v>
       </c>
       <c r="D102" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3614,13 +3623,13 @@
         <v>35</v>
       </c>
       <c r="B103" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C103" s="10">
         <v>41.82</v>
       </c>
       <c r="D103" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3628,13 +3637,13 @@
         <v>35</v>
       </c>
       <c r="B104" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C104" s="10">
         <v>197</v>
       </c>
       <c r="D104" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3642,13 +3651,13 @@
         <v>35</v>
       </c>
       <c r="B105" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C105" s="10">
         <v>25.84</v>
       </c>
       <c r="D105" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3656,13 +3665,13 @@
         <v>35</v>
       </c>
       <c r="B106" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C106" s="10">
         <v>191.9</v>
       </c>
       <c r="D106" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3670,13 +3679,13 @@
         <v>35</v>
       </c>
       <c r="B107" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C107" s="10">
         <v>111</v>
       </c>
       <c r="D107" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3684,13 +3693,13 @@
         <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C108" s="10">
         <v>65</v>
       </c>
       <c r="D108" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3698,13 +3707,13 @@
         <v>35</v>
       </c>
       <c r="B109" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C109" s="10">
         <v>65</v>
       </c>
       <c r="D109" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="110" ht="16.5" customHeight="1" spans="1:4">
@@ -3718,7 +3727,7 @@
     </row>
     <row r="112" ht="15" customHeight="1" spans="1:4">
       <c r="B112" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C112" s="13">
         <f>C87+C110</f>
@@ -3727,7 +3736,7 @@
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="189">
   <si>
     <t>梦幻西游 · 支出明细表（当前新号账期｜黄色行为新增录入区）</t>
   </si>
@@ -76,6 +76,9 @@
     <t>地府男魔</t>
   </si>
   <si>
+    <t>化生摆摊号</t>
+  </si>
+  <si>
     <t>角色账号购置 小计</t>
   </si>
   <si>
@@ -98,6 +101,9 @@
   </si>
   <si>
     <t>▌召唤兽采购</t>
+  </si>
+  <si>
+    <t>摆摊号月影仙</t>
   </si>
   <si>
     <t>召唤兽采购 小计</t>
@@ -1676,7 +1682,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1783,82 +1789,91 @@
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
       <c r="B9" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="12">
-        <f>SUM(C4:C8)</f>
-        <v>13000</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" spans="1:4">
-      <c r="A11" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" spans="1:4">
+      <c r="B10" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
+      <c r="C10" s="12">
+        <f>SUM(C4:C9)</f>
+        <v>13100</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:4">
+      <c r="A12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="10">
-        <v>20</v>
-      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="10">
         <v>300</v>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" spans="1:4">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="22">
+    <row r="15" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="22">
         <v>150</v>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" spans="1:4">
-      <c r="B15" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="12">
-        <f>SUM(C12:C14)</f>
+    <row r="16" ht="16.5" customHeight="1" spans="1:4">
+      <c r="B16" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="12">
+        <f>SUM(C13:C15)</f>
         <v>470</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:4">
-      <c r="A17" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
+    <row r="18" ht="15" customHeight="1" spans="1:4">
+      <c r="A18" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="19"/>
+      <c r="A19" s="19" t="s">
+        <v>22</v>
+      </c>
       <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
+      <c r="C19" s="19">
+        <v>50</v>
+      </c>
       <c r="D19" s="19"/>
     </row>
     <row r="20" spans="1:4">
@@ -1879,28 +1894,28 @@
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
     </row>
-    <row r="23" ht="16.5" customHeight="1" spans="1:4">
-      <c r="B23" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="12">
-        <f>SUM(C18:C22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" spans="1:4">
-      <c r="A25" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
+    <row r="23" spans="1:4">
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" spans="1:4">
+      <c r="B24" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="12">
+        <f>SUM(C19:C23)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:4">
+      <c r="A26" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="19"/>
@@ -1926,36 +1941,42 @@
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
     </row>
-    <row r="31" ht="16.5" customHeight="1" spans="1:4">
-      <c r="B31" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="12">
-        <f>SUM(C26:C30)</f>
+    <row r="31" spans="1:4">
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+    </row>
+    <row r="32" ht="16.5" customHeight="1" spans="1:4">
+      <c r="B32" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="12">
+        <f>SUM(C27:C31)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:3">
-      <c r="A33" t="s">
-        <v>24</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C33" s="16">
-        <f>C9+C15+C23+C31</f>
-        <v>13470</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
+    <row r="34" ht="15" customHeight="1" spans="1:3">
+      <c r="A34" t="s">
         <v>26</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="16">
+        <f>C10+C16+C24+C32</f>
+        <v>13620</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A36:D36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1976,15 +1997,15 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:4">
       <c r="A2" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>3</v>
@@ -1995,7 +2016,7 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:4">
       <c r="A3" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -2003,10 +2024,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" s="20">
         <v>12.25</v>
@@ -2057,7 +2078,7 @@
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:4">
       <c r="B12" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C12" s="12">
         <f>SUM(C4:C11)</f>
@@ -2066,7 +2087,7 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:4">
       <c r="A14" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -2074,10 +2095,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C15" s="20">
         <v>103</v>
@@ -2086,10 +2107,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C16" s="20">
         <v>12</v>
@@ -2098,10 +2119,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C17" s="20">
         <v>193</v>
@@ -2110,10 +2131,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C18" s="20">
         <v>194</v>
@@ -2123,13 +2144,13 @@
     <row r="19" spans="1:4">
       <c r="A19" s="19"/>
       <c r="B19" s="19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C19" s="20">
         <v>27</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2152,7 +2173,7 @@
     </row>
     <row r="23" ht="16.5" customHeight="1" spans="1:4">
       <c r="B23" s="11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C23" s="12">
         <f>SUM(C15:C22)</f>
@@ -2161,7 +2182,7 @@
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:4">
       <c r="A25" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -2169,10 +2190,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C26" s="20">
         <v>1850</v>
@@ -2181,10 +2202,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C27" s="20">
         <v>313</v>
@@ -2193,10 +2214,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C28" s="19">
         <v>843</v>
@@ -2205,10 +2226,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C29" s="19">
         <v>247</v>
@@ -2253,7 +2274,7 @@
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="1:4">
       <c r="B36" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C36" s="12">
         <f>SUM(C26:C35)</f>
@@ -2262,10 +2283,10 @@
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:4">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C38" s="16">
         <f>C12+C23+C36</f>
@@ -2274,7 +2295,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2300,104 +2321,104 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:3">
       <c r="A2" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B3" s="10">
-        <f>支出明细表!C33</f>
-        <v>13470</v>
+        <f>支出明细表!C34</f>
+        <v>13620</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B4" s="10">
         <f>游戏变现收入明细表!C38</f>
         <v>3794.25</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:3">
       <c r="A5" s="15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B5" s="16">
         <f>B3-B4</f>
-        <v>9675.75</v>
+        <v>9825.75</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:3">
       <c r="A7" s="18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B8" s="5">
         <v>4000.69</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B9" s="10">
         <f>B3+B8-B4</f>
-        <v>13676.44</v>
+        <v>13826.44</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:3">
       <c r="A10" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2424,55 +2445,55 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B5" s="5">
         <v>6455.7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B6" s="5">
         <v>2455.01</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B7" s="5">
         <v>4000.69</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:4">
@@ -2502,13 +2523,13 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C12" s="10">
         <v>391.9</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2516,13 +2537,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C13" s="10">
         <v>400</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2530,13 +2551,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C14" s="10">
         <v>519</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2544,13 +2565,13 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C15" s="10">
         <v>500</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2558,13 +2579,13 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C16" s="10">
         <v>866</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2572,18 +2593,18 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C17" s="10">
         <v>460</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:4">
       <c r="B18" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" s="12">
         <f>SUM(C12:C17)</f>
@@ -2592,7 +2613,7 @@
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:4">
       <c r="A20" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -2600,287 +2621,287 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C21" s="10">
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C22" s="10">
         <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C23" s="10">
         <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C24" s="10">
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C25" s="10">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C26" s="10">
         <v>10</v>
       </c>
       <c r="D26" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C27" s="10">
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C28" s="10">
         <v>300</v>
       </c>
       <c r="D28" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C29" s="10">
         <v>125</v>
       </c>
       <c r="D29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C30" s="10">
         <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C31" s="10">
         <v>1.05</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C32" s="10">
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C33" s="10">
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C34" s="10">
         <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C35" s="10">
         <v>290</v>
       </c>
       <c r="D35" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C36" s="10">
         <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C37" s="10">
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B38" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C38" s="10">
         <v>20</v>
       </c>
       <c r="D38" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C39" s="10">
         <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B40" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C40" s="10">
         <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:4">
       <c r="B41" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C41" s="12">
         <f>SUM(C21:C40)</f>
@@ -2889,7 +2910,7 @@
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:4">
       <c r="A43" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -2897,175 +2918,175 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B44" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C44" s="10">
         <v>128</v>
       </c>
       <c r="D44" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B45" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C45" s="10">
         <v>140</v>
       </c>
       <c r="D45" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C46" s="10">
         <v>120</v>
       </c>
       <c r="D46" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B47" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C47" s="10">
         <v>168</v>
       </c>
       <c r="D47" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B48" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C48" s="10">
         <v>106</v>
       </c>
       <c r="D48" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B49" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C49" s="10">
         <v>68.25</v>
       </c>
       <c r="D49" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B50" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C50" s="10">
         <v>65</v>
       </c>
       <c r="D50" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B51" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C51" s="10">
         <v>409</v>
       </c>
       <c r="D51" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B52" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C52" s="10">
         <v>177</v>
       </c>
       <c r="D52" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B53" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C53" s="10">
         <v>160</v>
       </c>
       <c r="D53" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C54" s="10">
         <v>210</v>
       </c>
       <c r="D54" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C55" s="10">
         <v>240</v>
       </c>
       <c r="D55" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56" ht="16.5" customHeight="1" spans="1:4">
       <c r="B56" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C56" s="12">
         <f>SUM(C44:C55)</f>
@@ -3074,7 +3095,7 @@
     </row>
     <row r="58" ht="15" customHeight="1" spans="1:4">
       <c r="A58" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
@@ -3082,105 +3103,105 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B59" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C59" s="10">
         <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C60" s="10">
         <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B61" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C61" s="10">
         <v>40.5</v>
       </c>
       <c r="D61" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B62" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C62" s="10">
         <v>109</v>
       </c>
       <c r="D62" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B63" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C63" s="10">
         <v>48</v>
       </c>
       <c r="D63" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B64" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C64" s="10">
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B65" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C65" s="10">
         <v>10</v>
       </c>
       <c r="D65" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="66" ht="16.5" customHeight="1" spans="1:4">
       <c r="B66" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C66" s="12">
         <f>SUM(C59:C65)</f>
@@ -3189,7 +3210,7 @@
     </row>
     <row r="68" ht="15" customHeight="1" spans="1:4">
       <c r="B68" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C68" s="13">
         <f>C18+C41+C56+C66</f>
@@ -3198,15 +3219,15 @@
     </row>
     <row r="70" ht="18" customHeight="1" spans="1:4">
       <c r="A70" s="14" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:4">
       <c r="A71" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C71" s="7" t="s">
         <v>3</v>
@@ -3217,7 +3238,7 @@
     </row>
     <row r="72" ht="15" customHeight="1" spans="1:4">
       <c r="A72" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B72" s="9"/>
       <c r="C72" s="9"/>
@@ -3225,203 +3246,203 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B73" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C73" s="10">
         <v>85.5</v>
       </c>
       <c r="D73" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B74" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C74" s="10">
         <v>161.5</v>
       </c>
       <c r="D74" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B75" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C75" s="10">
         <v>123.5</v>
       </c>
       <c r="D75" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B76" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C76" s="10">
         <v>9.5</v>
       </c>
       <c r="D76" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B77" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C77" s="10">
         <v>115</v>
       </c>
       <c r="D77" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B78" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C78" s="10">
         <v>9.5</v>
       </c>
       <c r="D78" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B79" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C79" s="10">
         <v>133</v>
       </c>
       <c r="D79" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B80" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C80" s="10">
         <v>66.5</v>
       </c>
       <c r="D80" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B81" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C81" s="10">
         <v>14.5</v>
       </c>
       <c r="D81" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B82" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C82" s="10">
         <v>14.5</v>
       </c>
       <c r="D82" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B83" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C83" s="10">
         <v>9.5</v>
       </c>
       <c r="D83" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B84" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C84" s="10">
         <v>9.5</v>
       </c>
       <c r="D84" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B85" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C85" s="10">
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B86" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C86" s="10">
         <v>9.5</v>
       </c>
       <c r="D86" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="87" ht="16.5" customHeight="1" spans="1:4">
       <c r="B87" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C87" s="12">
         <f>SUM(C73:C86)</f>
@@ -3430,7 +3451,7 @@
     </row>
     <row r="89" ht="15" customHeight="1" spans="1:4">
       <c r="A89" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B89" s="9"/>
       <c r="C89" s="9"/>
@@ -3438,287 +3459,287 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B90" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C90" s="10">
         <v>202</v>
       </c>
       <c r="D90" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B91" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C91" s="10">
         <v>67.45</v>
       </c>
       <c r="D91" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B92" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C92" s="10">
         <v>67.45</v>
       </c>
       <c r="D92" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B93" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C93" s="10">
         <v>66.78</v>
       </c>
       <c r="D93" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B94" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C94" s="10">
         <v>66.78</v>
       </c>
       <c r="D94" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B95" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C95" s="10">
         <v>66.02</v>
       </c>
       <c r="D95" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B96" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C96" s="10">
         <v>65.55</v>
       </c>
       <c r="D96" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B97" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C97" s="10">
         <v>66.02</v>
       </c>
       <c r="D97" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B98" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C98" s="10">
         <v>69.2</v>
       </c>
       <c r="D98" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B99" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C99" s="10">
         <v>68</v>
       </c>
       <c r="D99" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B100" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C100" s="10">
         <v>41</v>
       </c>
       <c r="D100" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B101" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C101" s="10">
         <v>67.7</v>
       </c>
       <c r="D101" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B102" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C102" s="10">
         <v>68</v>
       </c>
       <c r="D102" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B103" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C103" s="10">
         <v>41.82</v>
       </c>
       <c r="D103" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B104" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C104" s="10">
         <v>197</v>
       </c>
       <c r="D104" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B105" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C105" s="10">
         <v>25.84</v>
       </c>
       <c r="D105" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B106" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C106" s="10">
         <v>191.9</v>
       </c>
       <c r="D106" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B107" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C107" s="10">
         <v>111</v>
       </c>
       <c r="D107" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B108" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C108" s="10">
         <v>65</v>
       </c>
       <c r="D108" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B109" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C109" s="10">
         <v>65</v>
       </c>
       <c r="D109" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="110" ht="16.5" customHeight="1" spans="1:4">
       <c r="B110" s="11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C110" s="12">
         <f>SUM(C90:C109)</f>
@@ -3727,7 +3748,7 @@
     </row>
     <row r="112" ht="15" customHeight="1" spans="1:4">
       <c r="B112" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C112" s="13">
         <f>C87+C110</f>
@@ -3736,7 +3757,7 @@
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="支出明细表" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="191">
   <si>
     <t>梦幻西游 · 支出明细表（当前新号账期｜黄色行为新增录入区）</t>
   </si>
@@ -151,7 +151,7 @@
     <t>物资变现</t>
   </si>
   <si>
-    <t>菜1</t>
+    <t>菜1 9月27</t>
   </si>
   <si>
     <t>胚涂山童</t>
@@ -167,6 +167,12 @@
   </si>
   <si>
     <t>9月27</t>
+  </si>
+  <si>
+    <t>男魔百亿高夜兽决</t>
+  </si>
+  <si>
+    <t>10月13（道人来之前）</t>
   </si>
   <si>
     <t>物资变现 小计</t>
@@ -2142,7 +2148,9 @@
       <c r="D18" s="19"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="19"/>
+      <c r="A19" s="19" t="s">
+        <v>37</v>
+      </c>
       <c r="B19" s="19" t="s">
         <v>42</v>
       </c>
@@ -2154,10 +2162,18 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
+      <c r="A20" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="19">
+        <v>160</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="19"/>
@@ -2173,16 +2189,16 @@
     </row>
     <row r="23" ht="16.5" customHeight="1" spans="1:4">
       <c r="B23" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C23" s="12">
         <f>SUM(C15:C22)</f>
-        <v>529</v>
+        <v>689</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:4">
       <c r="A25" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -2190,10 +2206,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C26" s="20">
         <v>1850</v>
@@ -2202,10 +2218,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C27" s="20">
         <v>313</v>
@@ -2214,10 +2230,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C28" s="19">
         <v>843</v>
@@ -2226,10 +2242,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C29" s="19">
         <v>247</v>
@@ -2274,7 +2290,7 @@
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="1:4">
       <c r="B36" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C36" s="12">
         <f>SUM(C26:C35)</f>
@@ -2283,19 +2299,19 @@
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:4">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C38" s="16">
         <f>C12+C23+C36</f>
-        <v>3794.25</v>
+        <v>3954.25</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -2321,104 +2337,104 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:3">
       <c r="A2" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B3" s="10">
         <f>支出明细表!C34</f>
         <v>13620</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B4" s="10">
         <f>游戏变现收入明细表!C38</f>
-        <v>3794.25</v>
+        <v>3954.25</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:3">
       <c r="A5" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" s="16">
         <f>B3-B4</f>
-        <v>9825.75</v>
+        <v>9665.75</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:3">
       <c r="A7" s="18" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B8" s="5">
         <v>4000.69</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B9" s="10">
         <f>B3+B8-B4</f>
-        <v>13826.44</v>
+        <v>13666.44</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:3">
       <c r="A10" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2445,55 +2461,55 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B5" s="5">
         <v>6455.7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B6" s="5">
         <v>2455.01</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B7" s="5">
         <v>4000.69</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:4">
@@ -2523,13 +2539,13 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C12" s="10">
         <v>391.9</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2537,13 +2553,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C13" s="10">
         <v>400</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2551,13 +2567,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C14" s="10">
         <v>519</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2565,13 +2581,13 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C15" s="10">
         <v>500</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2579,13 +2595,13 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C16" s="10">
         <v>866</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2593,13 +2609,13 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C17" s="10">
         <v>460</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:4">
@@ -2624,13 +2640,13 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C21" s="10">
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2638,13 +2654,13 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C22" s="10">
         <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2652,13 +2668,13 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C23" s="10">
         <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2666,13 +2682,13 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C24" s="10">
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2680,13 +2696,13 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C25" s="10">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2694,13 +2710,13 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C26" s="10">
         <v>10</v>
       </c>
       <c r="D26" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2708,13 +2724,13 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C27" s="10">
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2722,13 +2738,13 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C28" s="10">
         <v>300</v>
       </c>
       <c r="D28" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2736,13 +2752,13 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C29" s="10">
         <v>125</v>
       </c>
       <c r="D29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2750,13 +2766,13 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C30" s="10">
         <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2764,13 +2780,13 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C31" s="10">
         <v>1.05</v>
       </c>
       <c r="D31" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2778,13 +2794,13 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C32" s="10">
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2792,13 +2808,13 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C33" s="10">
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2806,13 +2822,13 @@
         <v>16</v>
       </c>
       <c r="B34" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C34" s="10">
         <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2820,13 +2836,13 @@
         <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C35" s="10">
         <v>290</v>
       </c>
       <c r="D35" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2834,13 +2850,13 @@
         <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C36" s="10">
         <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2848,13 +2864,13 @@
         <v>16</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C37" s="10">
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2862,13 +2878,13 @@
         <v>16</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C38" s="10">
         <v>20</v>
       </c>
       <c r="D38" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2876,13 +2892,13 @@
         <v>16</v>
       </c>
       <c r="B39" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C39" s="10">
         <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2890,13 +2906,13 @@
         <v>16</v>
       </c>
       <c r="B40" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C40" s="10">
         <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:4">
@@ -2918,170 +2934,170 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B44" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C44" s="10">
         <v>128</v>
       </c>
       <c r="D44" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B45" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C45" s="10">
         <v>140</v>
       </c>
       <c r="D45" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B46" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C46" s="10">
         <v>120</v>
       </c>
       <c r="D46" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B47" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C47" s="10">
         <v>168</v>
       </c>
       <c r="D47" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B48" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C48" s="10">
         <v>106</v>
       </c>
       <c r="D48" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B49" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C49" s="10">
         <v>68.25</v>
       </c>
       <c r="D49" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B50" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C50" s="10">
         <v>65</v>
       </c>
       <c r="D50" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B51" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C51" s="10">
         <v>409</v>
       </c>
       <c r="D51" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B52" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C52" s="10">
         <v>177</v>
       </c>
       <c r="D52" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B53" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C53" s="10">
         <v>160</v>
       </c>
       <c r="D53" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B54" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C54" s="10">
         <v>210</v>
       </c>
       <c r="D54" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B55" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C55" s="10">
         <v>240</v>
       </c>
       <c r="D55" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56" ht="16.5" customHeight="1" spans="1:4">
@@ -3106,13 +3122,13 @@
         <v>26</v>
       </c>
       <c r="B59" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C59" s="10">
         <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3120,13 +3136,13 @@
         <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C60" s="10">
         <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3134,13 +3150,13 @@
         <v>26</v>
       </c>
       <c r="B61" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C61" s="10">
         <v>40.5</v>
       </c>
       <c r="D61" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3148,13 +3164,13 @@
         <v>26</v>
       </c>
       <c r="B62" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C62" s="10">
         <v>109</v>
       </c>
       <c r="D62" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3162,13 +3178,13 @@
         <v>26</v>
       </c>
       <c r="B63" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C63" s="10">
         <v>48</v>
       </c>
       <c r="D63" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3176,13 +3192,13 @@
         <v>26</v>
       </c>
       <c r="B64" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C64" s="10">
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3190,13 +3206,13 @@
         <v>26</v>
       </c>
       <c r="B65" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C65" s="10">
         <v>10</v>
       </c>
       <c r="D65" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="66" ht="16.5" customHeight="1" spans="1:4">
@@ -3210,7 +3226,7 @@
     </row>
     <row r="68" ht="15" customHeight="1" spans="1:4">
       <c r="B68" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C68" s="13">
         <f>C18+C41+C56+C66</f>
@@ -3219,7 +3235,7 @@
     </row>
     <row r="70" ht="18" customHeight="1" spans="1:4">
       <c r="A70" s="14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:4">
@@ -3246,198 +3262,198 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B73" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C73" s="10">
         <v>85.5</v>
       </c>
       <c r="D73" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B74" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C74" s="10">
         <v>161.5</v>
       </c>
       <c r="D74" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B75" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C75" s="10">
         <v>123.5</v>
       </c>
       <c r="D75" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B76" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C76" s="10">
         <v>9.5</v>
       </c>
       <c r="D76" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B77" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C77" s="10">
         <v>115</v>
       </c>
       <c r="D77" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B78" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C78" s="10">
         <v>9.5</v>
       </c>
       <c r="D78" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B79" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C79" s="10">
         <v>133</v>
       </c>
       <c r="D79" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B80" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C80" s="10">
         <v>66.5</v>
       </c>
       <c r="D80" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B81" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C81" s="10">
         <v>14.5</v>
       </c>
       <c r="D81" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B82" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C82" s="10">
         <v>14.5</v>
       </c>
       <c r="D82" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B83" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C83" s="10">
         <v>9.5</v>
       </c>
       <c r="D83" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B84" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C84" s="10">
         <v>9.5</v>
       </c>
       <c r="D84" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B85" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C85" s="10">
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B86" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C86" s="10">
         <v>9.5</v>
       </c>
       <c r="D86" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="87" ht="16.5" customHeight="1" spans="1:4">
@@ -3462,13 +3478,13 @@
         <v>37</v>
       </c>
       <c r="B90" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C90" s="10">
         <v>202</v>
       </c>
       <c r="D90" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3476,13 +3492,13 @@
         <v>37</v>
       </c>
       <c r="B91" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C91" s="10">
         <v>67.45</v>
       </c>
       <c r="D91" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3490,13 +3506,13 @@
         <v>37</v>
       </c>
       <c r="B92" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C92" s="10">
         <v>67.45</v>
       </c>
       <c r="D92" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3504,13 +3520,13 @@
         <v>37</v>
       </c>
       <c r="B93" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C93" s="10">
         <v>66.78</v>
       </c>
       <c r="D93" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3518,13 +3534,13 @@
         <v>37</v>
       </c>
       <c r="B94" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C94" s="10">
         <v>66.78</v>
       </c>
       <c r="D94" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3532,13 +3548,13 @@
         <v>37</v>
       </c>
       <c r="B95" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C95" s="10">
         <v>66.02</v>
       </c>
       <c r="D95" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3546,13 +3562,13 @@
         <v>37</v>
       </c>
       <c r="B96" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C96" s="10">
         <v>65.55</v>
       </c>
       <c r="D96" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3560,13 +3576,13 @@
         <v>37</v>
       </c>
       <c r="B97" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C97" s="10">
         <v>66.02</v>
       </c>
       <c r="D97" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3574,13 +3590,13 @@
         <v>37</v>
       </c>
       <c r="B98" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C98" s="10">
         <v>69.2</v>
       </c>
       <c r="D98" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3588,13 +3604,13 @@
         <v>37</v>
       </c>
       <c r="B99" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C99" s="10">
         <v>68</v>
       </c>
       <c r="D99" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3602,13 +3618,13 @@
         <v>37</v>
       </c>
       <c r="B100" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C100" s="10">
         <v>41</v>
       </c>
       <c r="D100" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3616,13 +3632,13 @@
         <v>37</v>
       </c>
       <c r="B101" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C101" s="10">
         <v>67.7</v>
       </c>
       <c r="D101" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3630,13 +3646,13 @@
         <v>37</v>
       </c>
       <c r="B102" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C102" s="10">
         <v>68</v>
       </c>
       <c r="D102" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3644,13 +3660,13 @@
         <v>37</v>
       </c>
       <c r="B103" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C103" s="10">
         <v>41.82</v>
       </c>
       <c r="D103" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3658,13 +3674,13 @@
         <v>37</v>
       </c>
       <c r="B104" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C104" s="10">
         <v>197</v>
       </c>
       <c r="D104" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3672,13 +3688,13 @@
         <v>37</v>
       </c>
       <c r="B105" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C105" s="10">
         <v>25.84</v>
       </c>
       <c r="D105" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3686,13 +3702,13 @@
         <v>37</v>
       </c>
       <c r="B106" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C106" s="10">
         <v>191.9</v>
       </c>
       <c r="D106" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3700,13 +3716,13 @@
         <v>37</v>
       </c>
       <c r="B107" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C107" s="10">
         <v>111</v>
       </c>
       <c r="D107" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3714,13 +3730,13 @@
         <v>37</v>
       </c>
       <c r="B108" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C108" s="10">
         <v>65</v>
       </c>
       <c r="D108" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3728,18 +3744,18 @@
         <v>37</v>
       </c>
       <c r="B109" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C109" s="10">
         <v>65</v>
       </c>
       <c r="D109" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="110" ht="16.5" customHeight="1" spans="1:4">
       <c r="B110" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C110" s="12">
         <f>SUM(C90:C109)</f>
@@ -3748,7 +3764,7 @@
     </row>
     <row r="112" ht="15" customHeight="1" spans="1:4">
       <c r="B112" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C112" s="13">
         <f>C87+C110</f>
@@ -3757,7 +3773,7 @@
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="1"/>
   </bookViews>
   <sheets>
     <sheet name="支出明细表" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="203">
   <si>
     <t>梦幻西游 · 支出明细表（当前新号账期｜黄色行为新增录入区）</t>
   </si>
@@ -79,6 +79,15 @@
     <t>化生摆摊号</t>
   </si>
   <si>
+    <t>B新号（含装备/召唤兽）</t>
+  </si>
+  <si>
+    <t>角色账号购置B</t>
+  </si>
+  <si>
+    <t>地府老虎</t>
+  </si>
+  <si>
     <t>角色账号购置 小计</t>
   </si>
   <si>
@@ -97,6 +106,18 @@
     <t>10月8号补点卡</t>
   </si>
   <si>
+    <t>B组点卡</t>
+  </si>
+  <si>
+    <t>100启动</t>
+  </si>
+  <si>
+    <t>A点卡</t>
+  </si>
+  <si>
+    <t>10月19补100</t>
+  </si>
+  <si>
     <t>点卡相关 小计</t>
   </si>
   <si>
@@ -175,6 +196,9 @@
     <t>10月13（道人来之前）</t>
   </si>
   <si>
+    <t>出菜 10月14</t>
+  </si>
+  <si>
     <t>物资变现 小计</t>
   </si>
   <si>
@@ -196,6 +220,15 @@
     <t>10月10号结算(247雷鸟人须弥</t>
   </si>
   <si>
+    <t>10月15号结算（男魔 搞·不赢 360)</t>
+  </si>
+  <si>
+    <t>10月17 结算（要·不起360)</t>
+  </si>
+  <si>
+    <t>环装</t>
+  </si>
+  <si>
     <t>旧号回笼 小计</t>
   </si>
   <si>
@@ -241,7 +274,10 @@
     <t>见「历史坏账归档」｜支出 6455.7 − 已变现 2455.01</t>
   </si>
   <si>
-    <t>全实际净投入</t>
+    <t>旧号坏账冲回</t>
+  </si>
+  <si>
+    <t>旧号净投入</t>
   </si>
   <si>
     <t>📌 补充说明</t>
@@ -1688,7 +1724,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1804,124 +1840,178 @@
       <c r="C9" s="12">
         <v>100</v>
       </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="10" ht="16.5" customHeight="1" spans="1:4">
-      <c r="B10" s="11" t="s">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="12">
+        <v>460</v>
+      </c>
+      <c r="D10" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="12">
-        <f>SUM(C4:C9)</f>
-        <v>13100</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="1:4">
-      <c r="A12" s="8" t="s">
+    </row>
+    <row r="11" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="12">
+        <v>460</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="12">
+        <v>460</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" spans="1:4">
       <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" s="12">
+        <v>460</v>
+      </c>
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="12">
+        <v>460</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" customHeight="1" spans="1:4">
+      <c r="B15" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C15" s="12">
+        <f>SUM(C4:C14)</f>
+        <v>15400</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:4">
+      <c r="A17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="10">
+      <c r="C18" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="10">
         <v>300</v>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" spans="1:4">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="21" t="s">
+    <row r="20" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="22">
+      <c r="B20" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="22">
         <v>150</v>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" spans="1:4">
-      <c r="B16" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="12">
-        <f>SUM(C13:C15)</f>
-        <v>470</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" spans="1:4">
-      <c r="A18" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19">
+    <row r="21" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" customHeight="1" spans="1:4">
+      <c r="B23" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="12">
+        <f>SUM(C18:C22)</f>
+        <v>670</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:4">
+      <c r="A25" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19">
         <v>50</v>
       </c>
-      <c r="D19" s="19"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-    </row>
-    <row r="24" ht="16.5" customHeight="1" spans="1:4">
-      <c r="B24" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="12">
-        <f>SUM(C19:C23)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" spans="1:4">
-      <c r="A26" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
+      <c r="D26" s="19"/>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="19"/>
@@ -1947,42 +2037,83 @@
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
     </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-    </row>
-    <row r="32" ht="16.5" customHeight="1" spans="1:4">
-      <c r="B32" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C32" s="12">
-        <f>SUM(C27:C31)</f>
+    <row r="31" ht="16.5" customHeight="1" spans="1:4">
+      <c r="B31" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="12">
+        <f>SUM(C26:C30)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" spans="1:4">
+      <c r="A33" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="19"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="19"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="19"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="19"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+    </row>
+    <row r="39" ht="16.5" customHeight="1" spans="1:4">
+      <c r="B39" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="12">
+        <f>SUM(C34:C38)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:3">
-      <c r="A34" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C34" s="16">
-        <f>C10+C16+C24+C32</f>
-        <v>13620</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>28</v>
+    <row r="41" ht="15" customHeight="1" spans="1:4">
+      <c r="A41" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" s="16">
+        <f>C15+C23+C31+C39</f>
+        <v>16120</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A43:D43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2003,15 +2134,15 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:4">
       <c r="A2" s="7" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>3</v>
@@ -2022,7 +2153,7 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:4">
       <c r="A3" s="8" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -2030,10 +2161,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="19" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C4" s="20">
         <v>12.25</v>
@@ -2084,7 +2215,7 @@
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:4">
       <c r="B12" s="11" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C12" s="12">
         <f>SUM(C4:C11)</f>
@@ -2093,7 +2224,7 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:4">
       <c r="A14" s="8" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -2101,10 +2232,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="19" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C15" s="20">
         <v>103</v>
@@ -2113,10 +2244,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="19" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C16" s="20">
         <v>12</v>
@@ -2125,10 +2256,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="19" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C17" s="20">
         <v>193</v>
@@ -2137,10 +2268,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="19" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C18" s="20">
         <v>194</v>
@@ -2149,36 +2280,42 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="19" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C19" s="20">
         <v>27</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="19" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C20" s="19">
         <v>160</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
+      <c r="A21" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="19">
+        <v>198</v>
+      </c>
       <c r="D21" s="19"/>
     </row>
     <row r="22" spans="1:4">
@@ -2189,16 +2326,16 @@
     </row>
     <row r="23" ht="16.5" customHeight="1" spans="1:4">
       <c r="B23" s="11" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C23" s="12">
         <f>SUM(C15:C22)</f>
-        <v>689</v>
+        <v>887</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:4">
       <c r="A25" s="8" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -2206,10 +2343,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="19" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C26" s="20">
         <v>1850</v>
@@ -2218,10 +2355,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="19" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C27" s="20">
         <v>313</v>
@@ -2230,10 +2367,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="19" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C28" s="19">
         <v>843</v>
@@ -2242,10 +2379,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="19" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C29" s="19">
         <v>247</v>
@@ -2253,21 +2390,39 @@
       <c r="D29" s="19"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
+      <c r="A30" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="19">
+        <v>360</v>
+      </c>
       <c r="D30" s="19"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
+      <c r="A31" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="19">
+        <v>360</v>
+      </c>
       <c r="D31" s="19"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
+      <c r="A32" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="19">
+        <v>8.5</v>
+      </c>
       <c r="D32" s="19"/>
     </row>
     <row r="33" spans="1:4">
@@ -2290,28 +2445,28 @@
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="1:4">
       <c r="B36" s="11" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C36" s="12">
         <f>SUM(C26:C35)</f>
-        <v>3253</v>
+        <v>3981.5</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:4">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C38" s="16">
         <f>C12+C23+C36</f>
-        <v>3954.25</v>
+        <v>4880.75</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2327,7 +2482,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -2337,104 +2492,113 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:3">
       <c r="A2" s="7" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B3" s="10">
-        <f>支出明细表!C34</f>
-        <v>13620</v>
+        <f>支出明细表!C41</f>
+        <v>16120</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B4" s="10">
-        <f>游戏变现收入明细表!C38</f>
-        <v>3954.25</v>
+        <f>游戏变现收入明细表!C23</f>
+        <v>887</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:3">
       <c r="A5" s="15" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B5" s="16">
         <f>B3-B4</f>
-        <v>9665.75</v>
+        <v>15233</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:3">
       <c r="A7" s="18" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B8" s="5">
         <v>4000.69</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:3">
       <c r="A9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="10">
-        <f>B3+B8-B4</f>
-        <v>13666.44</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="1:3">
-      <c r="A10" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>70</v>
+        <v>79</v>
+      </c>
+      <c r="B9" s="12">
+        <f>游戏变现收入明细表!C36</f>
+        <v>3981.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="10">
+        <f>B8-B9</f>
+        <v>19.1900000000001</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:3">
+      <c r="A11" s="3" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2461,55 +2625,55 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B5" s="5">
         <v>6455.7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B6" s="5">
         <v>2455.01</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B7" s="5">
         <v>4000.69</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:4">
@@ -2539,13 +2703,13 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C12" s="10">
         <v>391.9</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2553,13 +2717,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C13" s="10">
         <v>400</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2567,13 +2731,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C14" s="10">
         <v>519</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2581,13 +2745,13 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C15" s="10">
         <v>500</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2595,13 +2759,13 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C16" s="10">
         <v>866</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2609,18 +2773,18 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C17" s="10">
         <v>460</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:4">
       <c r="B18" s="11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C18" s="12">
         <f>SUM(C12:C17)</f>
@@ -2629,7 +2793,7 @@
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:4">
       <c r="A20" s="8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -2637,287 +2801,287 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C21" s="10">
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C22" s="10">
         <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="C23" s="10">
         <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="C24" s="10">
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="C25" s="10">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C26" s="10">
         <v>10</v>
       </c>
       <c r="D26" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C27" s="10">
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C28" s="10">
         <v>300</v>
       </c>
       <c r="D28" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C29" s="10">
         <v>125</v>
       </c>
       <c r="D29" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="C30" s="10">
         <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C31" s="10">
         <v>1.05</v>
       </c>
       <c r="D31" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="C32" s="10">
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="C33" s="10">
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C34" s="10">
         <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="C35" s="10">
         <v>290</v>
       </c>
       <c r="D35" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C36" s="10">
         <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="C37" s="10">
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C38" s="10">
         <v>20</v>
       </c>
       <c r="D38" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C39" s="10">
         <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C40" s="10">
         <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:4">
       <c r="B41" s="11" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C41" s="12">
         <f>SUM(C21:C40)</f>
@@ -2926,7 +3090,7 @@
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:4">
       <c r="A43" s="8" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -2934,175 +3098,175 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B44" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C44" s="10">
         <v>128</v>
       </c>
       <c r="D44" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B45" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="C45" s="10">
         <v>140</v>
       </c>
       <c r="D45" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B46" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="C46" s="10">
         <v>120</v>
       </c>
       <c r="D46" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B47" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="C47" s="10">
         <v>168</v>
       </c>
       <c r="D47" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B48" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="C48" s="10">
         <v>106</v>
       </c>
       <c r="D48" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B49" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="C49" s="10">
         <v>68.25</v>
       </c>
       <c r="D49" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B50" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="C50" s="10">
         <v>65</v>
       </c>
       <c r="D50" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B51" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C51" s="10">
         <v>409</v>
       </c>
       <c r="D51" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B52" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C52" s="10">
         <v>177</v>
       </c>
       <c r="D52" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B53" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C53" s="10">
         <v>160</v>
       </c>
       <c r="D53" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B54" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="C54" s="10">
         <v>210</v>
       </c>
       <c r="D54" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B55" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="C55" s="10">
         <v>240</v>
       </c>
       <c r="D55" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" ht="16.5" customHeight="1" spans="1:4">
       <c r="B56" s="11" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C56" s="12">
         <f>SUM(C44:C55)</f>
@@ -3111,7 +3275,7 @@
     </row>
     <row r="58" ht="15" customHeight="1" spans="1:4">
       <c r="A58" s="8" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
@@ -3119,105 +3283,105 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B59" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="C59" s="10">
         <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B60" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C60" s="10">
         <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B61" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="C61" s="10">
         <v>40.5</v>
       </c>
       <c r="D61" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="C62" s="10">
         <v>109</v>
       </c>
       <c r="D62" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B63" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C63" s="10">
         <v>48</v>
       </c>
       <c r="D63" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="C64" s="10">
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B65" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="C65" s="10">
         <v>10</v>
       </c>
       <c r="D65" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="66" ht="16.5" customHeight="1" spans="1:4">
       <c r="B66" s="11" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C66" s="12">
         <f>SUM(C59:C65)</f>
@@ -3226,7 +3390,7 @@
     </row>
     <row r="68" ht="15" customHeight="1" spans="1:4">
       <c r="B68" s="3" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C68" s="13">
         <f>C18+C41+C56+C66</f>
@@ -3235,15 +3399,15 @@
     </row>
     <row r="70" ht="18" customHeight="1" spans="1:4">
       <c r="A70" s="14" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:4">
       <c r="A71" s="7" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C71" s="7" t="s">
         <v>3</v>
@@ -3254,7 +3418,7 @@
     </row>
     <row r="72" ht="15" customHeight="1" spans="1:4">
       <c r="A72" s="8" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B72" s="9"/>
       <c r="C72" s="9"/>
@@ -3262,203 +3426,203 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B73" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C73" s="10">
         <v>85.5</v>
       </c>
       <c r="D73" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B74" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C74" s="10">
         <v>161.5</v>
       </c>
       <c r="D74" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B75" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="C75" s="10">
         <v>123.5</v>
       </c>
       <c r="D75" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B76" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C76" s="10">
         <v>9.5</v>
       </c>
       <c r="D76" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B77" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C77" s="10">
         <v>115</v>
       </c>
       <c r="D77" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B78" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="C78" s="10">
         <v>9.5</v>
       </c>
       <c r="D78" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B79" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C79" s="10">
         <v>133</v>
       </c>
       <c r="D79" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B80" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C80" s="10">
         <v>66.5</v>
       </c>
       <c r="D80" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B81" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C81" s="10">
         <v>14.5</v>
       </c>
       <c r="D81" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B82" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="C82" s="10">
         <v>14.5</v>
       </c>
       <c r="D82" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B83" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="C83" s="10">
         <v>9.5</v>
       </c>
       <c r="D83" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B84" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="C84" s="10">
         <v>9.5</v>
       </c>
       <c r="D84" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B85" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="C85" s="10">
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B86" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C86" s="10">
         <v>9.5</v>
       </c>
       <c r="D86" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="87" ht="16.5" customHeight="1" spans="1:4">
       <c r="B87" s="11" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C87" s="12">
         <f>SUM(C73:C86)</f>
@@ -3467,7 +3631,7 @@
     </row>
     <row r="89" ht="15" customHeight="1" spans="1:4">
       <c r="A89" s="8" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B89" s="9"/>
       <c r="C89" s="9"/>
@@ -3475,287 +3639,287 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B90" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="C90" s="10">
         <v>202</v>
       </c>
       <c r="D90" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B91" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="C91" s="10">
         <v>67.45</v>
       </c>
       <c r="D91" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B92" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="C92" s="10">
         <v>67.45</v>
       </c>
       <c r="D92" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B93" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="C93" s="10">
         <v>66.78</v>
       </c>
       <c r="D93" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B94" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="C94" s="10">
         <v>66.78</v>
       </c>
       <c r="D94" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B95" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="C95" s="10">
         <v>66.02</v>
       </c>
       <c r="D95" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B96" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="C96" s="10">
         <v>65.55</v>
       </c>
       <c r="D96" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B97" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="C97" s="10">
         <v>66.02</v>
       </c>
       <c r="D97" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B98" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="C98" s="10">
         <v>69.2</v>
       </c>
       <c r="D98" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B99" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="C99" s="10">
         <v>68</v>
       </c>
       <c r="D99" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B100" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C100" s="10">
         <v>41</v>
       </c>
       <c r="D100" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B101" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C101" s="10">
         <v>67.7</v>
       </c>
       <c r="D101" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B102" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="C102" s="10">
         <v>68</v>
       </c>
       <c r="D102" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B103" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C103" s="10">
         <v>41.82</v>
       </c>
       <c r="D103" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B104" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C104" s="10">
         <v>197</v>
       </c>
       <c r="D104" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B105" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="C105" s="10">
         <v>25.84</v>
       </c>
       <c r="D105" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B106" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C106" s="10">
         <v>191.9</v>
       </c>
       <c r="D106" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B107" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="C107" s="10">
         <v>111</v>
       </c>
       <c r="D107" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B108" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C108" s="10">
         <v>65</v>
       </c>
       <c r="D108" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B109" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="C109" s="10">
         <v>65</v>
       </c>
       <c r="D109" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="110" ht="16.5" customHeight="1" spans="1:4">
       <c r="B110" s="11" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C110" s="12">
         <f>SUM(C90:C109)</f>
@@ -3764,7 +3928,7 @@
     </row>
     <row r="112" ht="15" customHeight="1" spans="1:4">
       <c r="B112" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="C112" s="13">
         <f>C87+C110</f>
@@ -3773,7 +3937,7 @@
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="支出明细表" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="207">
   <si>
     <t>梦幻西游 · 支出明细表（当前新号账期｜黄色行为新增录入区）</t>
   </si>
@@ -163,6 +163,15 @@
     <t>9月29</t>
   </si>
   <si>
+    <t>月影仙卖出</t>
+  </si>
+  <si>
+    <t>10月19</t>
+  </si>
+  <si>
+    <t>亏手续费</t>
+  </si>
+  <si>
     <t>宠物变现 小计</t>
   </si>
   <si>
@@ -227,6 +236,9 @@
   </si>
   <si>
     <t>环装</t>
+  </si>
+  <si>
+    <t>10月19 结算 (阳光女号)</t>
   </si>
   <si>
     <t>旧号回笼 小计</t>
@@ -2172,10 +2184,18 @@
       <c r="D4" s="19"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
+      <c r="A5" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="19">
+        <v>47.5</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="19"/>
@@ -2215,16 +2235,16 @@
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:4">
       <c r="B12" s="11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C12" s="12">
         <f>SUM(C4:C11)</f>
-        <v>12.25</v>
+        <v>59.75</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:4">
       <c r="A14" s="8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -2232,10 +2252,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C15" s="20">
         <v>103</v>
@@ -2244,10 +2264,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C16" s="20">
         <v>12</v>
@@ -2256,10 +2276,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C17" s="20">
         <v>193</v>
@@ -2268,10 +2288,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C18" s="20">
         <v>194</v>
@@ -2280,38 +2300,38 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C19" s="20">
         <v>27</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C20" s="19">
         <v>160</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C21" s="19">
         <v>198</v>
@@ -2326,7 +2346,7 @@
     </row>
     <row r="23" ht="16.5" customHeight="1" spans="1:4">
       <c r="B23" s="11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C23" s="12">
         <f>SUM(C15:C22)</f>
@@ -2335,7 +2355,7 @@
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:4">
       <c r="A25" s="8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -2343,10 +2363,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C26" s="20">
         <v>1850</v>
@@ -2355,10 +2375,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C27" s="20">
         <v>313</v>
@@ -2367,10 +2387,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C28" s="19">
         <v>843</v>
@@ -2379,10 +2399,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C29" s="19">
         <v>247</v>
@@ -2391,10 +2411,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C30" s="19">
         <v>360</v>
@@ -2403,10 +2423,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C31" s="19">
         <v>360</v>
@@ -2415,10 +2435,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C32" s="19">
         <v>8.5</v>
@@ -2426,9 +2446,15 @@
       <c r="D32" s="19"/>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
+      <c r="A33" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="19">
+        <v>328</v>
+      </c>
       <c r="D33" s="19"/>
     </row>
     <row r="34" spans="1:4">
@@ -2445,28 +2471,28 @@
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="1:4">
       <c r="B36" s="11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C36" s="12">
         <f>SUM(C26:C35)</f>
-        <v>3981.5</v>
+        <v>4309.5</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:4">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C38" s="16">
         <f>C12+C23+C36</f>
-        <v>4880.75</v>
+        <v>5256.25</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2492,113 +2518,113 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:3">
       <c r="A2" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B3" s="10">
         <f>支出明细表!C41</f>
         <v>16120</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B4" s="10">
         <f>游戏变现收入明细表!C23</f>
         <v>887</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:3">
       <c r="A5" s="15" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B5" s="16">
         <f>B3-B4</f>
         <v>15233</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:3">
       <c r="A7" s="18" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B8" s="5">
         <v>4000.69</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:3">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B9" s="12">
         <f>游戏变现收入明细表!C36</f>
-        <v>3981.5</v>
+        <v>4309.5</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B10" s="10">
         <f>B8-B9</f>
-        <v>19.1900000000001</v>
+        <v>-308.81</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2625,55 +2651,55 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B5" s="5">
         <v>6455.7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B6" s="5">
         <v>2455.01</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B7" s="5">
         <v>4000.69</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:4">
@@ -2703,13 +2729,13 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C12" s="10">
         <v>391.9</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2717,13 +2743,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C13" s="10">
         <v>400</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2731,13 +2757,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C14" s="10">
         <v>519</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2745,13 +2771,13 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C15" s="10">
         <v>500</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2759,13 +2785,13 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C16" s="10">
         <v>866</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2773,13 +2799,13 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C17" s="10">
         <v>460</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:4">
@@ -2804,13 +2830,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C21" s="10">
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2818,13 +2844,13 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C22" s="10">
         <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2832,13 +2858,13 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C23" s="10">
         <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2846,13 +2872,13 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C24" s="10">
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2860,13 +2886,13 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C25" s="10">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2874,13 +2900,13 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C26" s="10">
         <v>10</v>
       </c>
       <c r="D26" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2888,13 +2914,13 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C27" s="10">
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2902,13 +2928,13 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C28" s="10">
         <v>300</v>
       </c>
       <c r="D28" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2916,13 +2942,13 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C29" s="10">
         <v>125</v>
       </c>
       <c r="D29" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2930,13 +2956,13 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C30" s="10">
         <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2944,13 +2970,13 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C31" s="10">
         <v>1.05</v>
       </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2958,13 +2984,13 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C32" s="10">
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2972,13 +2998,13 @@
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C33" s="10">
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2986,13 +3012,13 @@
         <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C34" s="10">
         <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3000,13 +3026,13 @@
         <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C35" s="10">
         <v>290</v>
       </c>
       <c r="D35" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -3014,13 +3040,13 @@
         <v>19</v>
       </c>
       <c r="B36" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C36" s="10">
         <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -3028,13 +3054,13 @@
         <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C37" s="10">
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3042,13 +3068,13 @@
         <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C38" s="10">
         <v>20</v>
       </c>
       <c r="D38" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3056,13 +3082,13 @@
         <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C39" s="10">
         <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3070,13 +3096,13 @@
         <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C40" s="10">
         <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:4">
@@ -3098,170 +3124,170 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B44" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C44" s="10">
         <v>128</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B45" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C45" s="10">
         <v>140</v>
       </c>
       <c r="D45" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B46" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C46" s="10">
         <v>120</v>
       </c>
       <c r="D46" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B47" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C47" s="10">
         <v>168</v>
       </c>
       <c r="D47" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B48" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C48" s="10">
         <v>106</v>
       </c>
       <c r="D48" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B49" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C49" s="10">
         <v>68.25</v>
       </c>
       <c r="D49" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B50" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C50" s="10">
         <v>65</v>
       </c>
       <c r="D50" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B51" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C51" s="10">
         <v>409</v>
       </c>
       <c r="D51" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B52" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C52" s="10">
         <v>177</v>
       </c>
       <c r="D52" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B53" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C53" s="10">
         <v>160</v>
       </c>
       <c r="D53" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B54" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C54" s="10">
         <v>210</v>
       </c>
       <c r="D54" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B55" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C55" s="10">
         <v>240</v>
       </c>
       <c r="D55" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56" ht="16.5" customHeight="1" spans="1:4">
@@ -3286,13 +3312,13 @@
         <v>33</v>
       </c>
       <c r="B59" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C59" s="10">
         <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3300,13 +3326,13 @@
         <v>33</v>
       </c>
       <c r="B60" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C60" s="10">
         <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3314,13 +3340,13 @@
         <v>33</v>
       </c>
       <c r="B61" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C61" s="10">
         <v>40.5</v>
       </c>
       <c r="D61" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3328,13 +3354,13 @@
         <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C62" s="10">
         <v>109</v>
       </c>
       <c r="D62" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3342,13 +3368,13 @@
         <v>33</v>
       </c>
       <c r="B63" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C63" s="10">
         <v>48</v>
       </c>
       <c r="D63" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3356,13 +3382,13 @@
         <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C64" s="10">
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3370,13 +3396,13 @@
         <v>33</v>
       </c>
       <c r="B65" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C65" s="10">
         <v>10</v>
       </c>
       <c r="D65" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66" ht="16.5" customHeight="1" spans="1:4">
@@ -3390,7 +3416,7 @@
     </row>
     <row r="68" ht="15" customHeight="1" spans="1:4">
       <c r="B68" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C68" s="13">
         <f>C18+C41+C56+C66</f>
@@ -3399,7 +3425,7 @@
     </row>
     <row r="70" ht="18" customHeight="1" spans="1:4">
       <c r="A70" s="14" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:4">
@@ -3426,203 +3452,203 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B73" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C73" s="10">
         <v>85.5</v>
       </c>
       <c r="D73" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B74" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C74" s="10">
         <v>161.5</v>
       </c>
       <c r="D74" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B75" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C75" s="10">
         <v>123.5</v>
       </c>
       <c r="D75" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B76" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C76" s="10">
         <v>9.5</v>
       </c>
       <c r="D76" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B77" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C77" s="10">
         <v>115</v>
       </c>
       <c r="D77" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B78" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C78" s="10">
         <v>9.5</v>
       </c>
       <c r="D78" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B79" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C79" s="10">
         <v>133</v>
       </c>
       <c r="D79" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B80" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C80" s="10">
         <v>66.5</v>
       </c>
       <c r="D80" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B81" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C81" s="10">
         <v>14.5</v>
       </c>
       <c r="D81" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B82" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C82" s="10">
         <v>14.5</v>
       </c>
       <c r="D82" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B83" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C83" s="10">
         <v>9.5</v>
       </c>
       <c r="D83" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B84" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C84" s="10">
         <v>9.5</v>
       </c>
       <c r="D84" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B85" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C85" s="10">
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B86" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C86" s="10">
         <v>9.5</v>
       </c>
       <c r="D86" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="87" ht="16.5" customHeight="1" spans="1:4">
       <c r="B87" s="11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C87" s="12">
         <f>SUM(C73:C86)</f>
@@ -3631,7 +3657,7 @@
     </row>
     <row r="89" ht="15" customHeight="1" spans="1:4">
       <c r="A89" s="8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B89" s="9"/>
       <c r="C89" s="9"/>
@@ -3639,287 +3665,287 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C90" s="10">
         <v>202</v>
       </c>
       <c r="D90" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C91" s="10">
         <v>67.45</v>
       </c>
       <c r="D91" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C92" s="10">
         <v>67.45</v>
       </c>
       <c r="D92" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C93" s="10">
         <v>66.78</v>
       </c>
       <c r="D93" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C94" s="10">
         <v>66.78</v>
       </c>
       <c r="D94" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B95" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C95" s="10">
         <v>66.02</v>
       </c>
       <c r="D95" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B96" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C96" s="10">
         <v>65.55</v>
       </c>
       <c r="D96" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B97" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C97" s="10">
         <v>66.02</v>
       </c>
       <c r="D97" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B98" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C98" s="10">
         <v>69.2</v>
       </c>
       <c r="D98" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B99" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C99" s="10">
         <v>68</v>
       </c>
       <c r="D99" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B100" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C100" s="10">
         <v>41</v>
       </c>
       <c r="D100" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B101" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C101" s="10">
         <v>67.7</v>
       </c>
       <c r="D101" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B102" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C102" s="10">
         <v>68</v>
       </c>
       <c r="D102" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B103" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C103" s="10">
         <v>41.82</v>
       </c>
       <c r="D103" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B104" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C104" s="10">
         <v>197</v>
       </c>
       <c r="D104" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B105" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C105" s="10">
         <v>25.84</v>
       </c>
       <c r="D105" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B106" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C106" s="10">
         <v>191.9</v>
       </c>
       <c r="D106" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B107" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C107" s="10">
         <v>111</v>
       </c>
       <c r="D107" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B108" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C108" s="10">
         <v>65</v>
       </c>
       <c r="D108" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B109" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C109" s="10">
         <v>65</v>
       </c>
       <c r="D109" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="110" ht="16.5" customHeight="1" spans="1:4">
       <c r="B110" s="11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C110" s="12">
         <f>SUM(C90:C109)</f>
@@ -3928,7 +3954,7 @@
     </row>
     <row r="112" ht="15" customHeight="1" spans="1:4">
       <c r="B112" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C112" s="13">
         <f>C87+C110</f>
@@ -3937,7 +3963,7 @@
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\MHXY\chenlong5469-ui.github.io\now\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\MHH\now\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17775" firstSheet="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="支出明细表" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="219">
   <si>
     <t>梦幻西游 · 支出明细表（当前新号账期｜黄色行为新增录入区）</t>
   </si>
@@ -232,6 +232,9 @@
     <t>出菜 10月20</t>
   </si>
   <si>
+    <t>10月22 小号组出菜</t>
+  </si>
+  <si>
     <t>物资变现 小计</t>
   </si>
   <si>
@@ -265,6 +268,9 @@
     <t>10月19 结算 (阳光女号)</t>
   </si>
   <si>
+    <t>10月23结算(1900攻击律法（血亏)</t>
+  </si>
+  <si>
     <t>旧号回笼 小计</t>
   </si>
   <si>
@@ -287,6 +293,9 @@
   </si>
   <si>
     <t>当前新号：账号（含装宠）、点卡、后续采购</t>
+  </si>
+  <si>
+    <t>加：历史账号脱手支出（收入）</t>
   </si>
   <si>
     <t>减：游戏变现总收入</t>
@@ -1994,7 +2003,7 @@
         <v>26</v>
       </c>
       <c r="C16" s="12">
-        <f xml:space="preserve">SUM(C4:C15)</f>
+        <f>SUM(C4:C15)</f>
         <v>16855</v>
       </c>
     </row>
@@ -2066,7 +2075,7 @@
         <v>34</v>
       </c>
       <c r="C24" s="12">
-        <f xml:space="preserve">SUM(C19:C23)</f>
+        <f>SUM(C19:C23)</f>
         <v>670</v>
       </c>
     </row>
@@ -2118,7 +2127,7 @@
         <v>37</v>
       </c>
       <c r="C32" s="12">
-        <f xml:space="preserve">SUM(C27:C31)</f>
+        <f>SUM(C27:C31)</f>
         <v>50</v>
       </c>
     </row>
@@ -2166,7 +2175,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="12">
-        <f xml:space="preserve">SUM(C35:C39)</f>
+        <f>SUM(C35:C39)</f>
         <v>0</v>
       </c>
     </row>
@@ -2179,7 +2188,7 @@
         <v>41</v>
       </c>
       <c r="C42" s="16">
-        <f xml:space="preserve">C16+C24+C32+C40</f>
+        <f>C16+C24+C32+C40</f>
         <v>17575</v>
       </c>
     </row>
@@ -2201,7 +2210,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2304,7 +2313,7 @@
         <v>52</v>
       </c>
       <c r="C12" s="12">
-        <f xml:space="preserve">SUM(C4:C11)</f>
+        <f>SUM(C4:C11)</f>
         <v>59.75</v>
       </c>
     </row>
@@ -2405,172 +2414,256 @@
       <c r="D21" s="22"/>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="22"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B23" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="22">
+      <c r="C23" s="22">
         <v>199</v>
       </c>
-      <c r="D22" s="22"/>
-    </row>
-    <row r="23" ht="16.5" customHeight="1" spans="1:4">
-      <c r="B23" s="11" t="s">
+      <c r="D23" s="22"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A24" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="C23" s="12">
-        <f xml:space="preserve">SUM(C15:C22)</f>
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" spans="1:4">
-      <c r="A25" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="23">
-        <v>1850</v>
-      </c>
+      <c r="C24" s="22">
+        <v>93.1</v>
+      </c>
+      <c r="D24" s="22"/>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
       <c r="D26" s="22"/>
     </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="B27" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="23">
-        <v>313</v>
-      </c>
+    <row r="27" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
       <c r="D27" s="22"/>
     </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="22">
-        <v>843</v>
-      </c>
+    <row r="28" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
       <c r="D28" s="22"/>
     </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" s="22">
-        <v>247</v>
-      </c>
+    <row r="29" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
       <c r="D29" s="22"/>
     </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" s="23">
-        <v>360</v>
-      </c>
+    <row r="30" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
       <c r="D30" s="22"/>
     </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="B31" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C31" s="23">
-        <v>360</v>
-      </c>
+    <row r="31" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
       <c r="D31" s="22"/>
     </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="23">
-        <v>8.5</v>
-      </c>
+    <row r="32" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
       <c r="D32" s="22"/>
     </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" s="23">
-        <v>328</v>
-      </c>
+    <row r="33" ht="16.5" customHeight="1" spans="1:4">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
       <c r="D33" s="22"/>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" ht="16.5" customHeight="1" spans="1:4">
       <c r="A34" s="22"/>
       <c r="B34" s="22"/>
       <c r="C34" s="22"/>
       <c r="D34" s="22"/>
     </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="22"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-    </row>
-    <row r="36" ht="16.5" customHeight="1" spans="1:4">
-      <c r="B36" s="11" t="s">
+    <row r="35" ht="16.5" customHeight="1" spans="1:4">
+      <c r="B35" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="12">
+        <f>SUM(C15:C34)</f>
+        <v>1179.1</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" spans="1:4">
+      <c r="A37" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="23">
+        <v>1850</v>
+      </c>
+      <c r="D38" s="22"/>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="23">
+        <v>313</v>
+      </c>
+      <c r="D39" s="22"/>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="22">
+        <v>843</v>
+      </c>
+      <c r="D40" s="22"/>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" s="22">
+        <v>247</v>
+      </c>
+      <c r="D41" s="22"/>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="23">
+        <v>360</v>
+      </c>
+      <c r="D42" s="22"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" s="23">
+        <v>360</v>
+      </c>
+      <c r="D43" s="22"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B44" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="23">
+        <v>8.5</v>
+      </c>
+      <c r="D44" s="22"/>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="12">
-        <f xml:space="preserve">SUM(C26:C35)</f>
-        <v>4309.5</v>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" spans="1:4">
-      <c r="A38" t="s">
-        <v>67</v>
-      </c>
-      <c r="B38" s="3" t="s">
+      <c r="C45" s="23">
+        <v>328</v>
+      </c>
+      <c r="D45" s="22"/>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B46" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="C38" s="16">
-        <f xml:space="preserve">C12+C23+C36</f>
-        <v>5455.25</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" t="s">
+      <c r="C46" s="22">
+        <v>105</v>
+      </c>
+      <c r="D46" s="22"/>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="22"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+    </row>
+    <row r="48" ht="16.5" customHeight="1" spans="1:4">
+      <c r="B48" s="11" t="s">
         <v>78</v>
+      </c>
+      <c r="C48" s="12">
+        <f>SUM(C38:C47)</f>
+        <v>4414.5</v>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1" spans="1:3">
+      <c r="A50" t="s">
+        <v>68</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C50" s="16">
+        <f>C12+C35+C48</f>
+        <v>5653.35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A52:D52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2580,7 +2673,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -2590,119 +2683,128 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:3">
       <c r="A2" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B3" s="10">
-        <f xml:space="preserve">支出明细表!C42</f>
+        <f>支出明细表!C42</f>
         <v>17575</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B4" s="10">
-        <f xml:space="preserve">游戏变现收入明细表!C12+游戏变现收入明细表!C23</f>
-        <v>1145.75</v>
-      </c>
-      <c r="C4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:3">
-      <c r="A5" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="16">
-        <f xml:space="preserve">B3-B4</f>
-        <v>16429.25</v>
-      </c>
-      <c r="C5" s="17" t="s">
+        <f>B11</f>
+        <v>-413.81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:3">
-      <c r="A7" s="18" t="s">
+      <c r="B5" s="10">
+        <f>游戏变现收入明细表!C12+游戏变现收入明细表!C35</f>
+        <v>1238.85</v>
+      </c>
+      <c r="C5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="4" t="s">
+    <row r="6" ht="15" customHeight="1" spans="1:3">
+      <c r="A6" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B6" s="16">
+        <f>B3+B4-B5</f>
+        <v>15922.34</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:3">
+      <c r="A8" s="18" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="5">
         <v>4000.69</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:3">
-      <c r="A9" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="13">
-        <f xml:space="preserve">游戏变现收入明细表!C36</f>
-        <v>4309.5</v>
+      <c r="C9" s="4" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:3">
-      <c r="A10" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="21">
-        <f xml:space="preserve">B8-B9</f>
-        <v>-308.81</v>
+      <c r="A10" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="13">
+        <f>游戏变现收入明细表!C48</f>
+        <v>4414.5</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:3">
-      <c r="A11" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>94</v>
+      <c r="A11" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="21">
+        <f>B9-B10</f>
+        <v>-413.81</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:3">
+      <c r="A12" s="3" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2723,55 +2825,55 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B5" s="5">
         <v>6455.7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B6" s="5">
         <v>2455.01</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B7" s="5">
         <v>4000.69</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:4">
@@ -2798,86 +2900,86 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C12" s="10">
         <v>391.9</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C13" s="10">
         <v>400</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C14" s="10">
         <v>519</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C15" s="10">
         <v>500</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C16" s="10">
         <v>866</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C17" s="10">
         <v>460</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:4">
@@ -2885,7 +2987,7 @@
         <v>26</v>
       </c>
       <c r="C18" s="12">
-        <f xml:space="preserve">SUM(C12:C17)</f>
+        <f>SUM(C12:C17)</f>
         <v>3136.9</v>
       </c>
     </row>
@@ -2902,13 +3004,13 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C21" s="10">
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2916,13 +3018,13 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C22" s="10">
         <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2930,13 +3032,13 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C23" s="10">
         <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2944,13 +3046,13 @@
         <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C24" s="10">
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2958,13 +3060,13 @@
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C25" s="10">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2972,13 +3074,13 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C26" s="10">
         <v>10</v>
       </c>
       <c r="D26" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2986,13 +3088,13 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C27" s="10">
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -3000,13 +3102,13 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C28" s="10">
         <v>300</v>
       </c>
       <c r="D28" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -3014,13 +3116,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C29" s="10">
         <v>125</v>
       </c>
       <c r="D29" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -3028,13 +3130,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C30" s="10">
         <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -3042,13 +3144,13 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C31" s="10">
         <v>1.05</v>
       </c>
       <c r="D31" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -3056,13 +3158,13 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C32" s="10">
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -3070,13 +3172,13 @@
         <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C33" s="10">
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -3084,13 +3186,13 @@
         <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C34" s="10">
         <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3098,13 +3200,13 @@
         <v>28</v>
       </c>
       <c r="B35" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C35" s="10">
         <v>290</v>
       </c>
       <c r="D35" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -3112,13 +3214,13 @@
         <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C36" s="10">
         <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -3126,13 +3228,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C37" s="10">
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3140,13 +3242,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C38" s="10">
         <v>20</v>
       </c>
       <c r="D38" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3154,13 +3256,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C39" s="10">
         <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3168,13 +3270,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C40" s="10">
         <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:4">
@@ -3182,7 +3284,7 @@
         <v>34</v>
       </c>
       <c r="C41" s="12">
-        <f xml:space="preserve">SUM(C21:C40)</f>
+        <f>SUM(C21:C40)</f>
         <v>1051.05</v>
       </c>
     </row>
@@ -3196,170 +3298,170 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B44" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C44" s="10">
         <v>128</v>
       </c>
       <c r="D44" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B45" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C45" s="10">
         <v>140</v>
       </c>
       <c r="D45" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B46" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C46" s="10">
         <v>120</v>
       </c>
       <c r="D46" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B47" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C47" s="10">
         <v>168</v>
       </c>
       <c r="D47" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B48" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C48" s="10">
         <v>106</v>
       </c>
       <c r="D48" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B49" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C49" s="10">
         <v>68.25</v>
       </c>
       <c r="D49" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B50" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C50" s="10">
         <v>65</v>
       </c>
       <c r="D50" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B51" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C51" s="10">
         <v>409</v>
       </c>
       <c r="D51" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B52" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C52" s="10">
         <v>177</v>
       </c>
       <c r="D52" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B53" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C53" s="10">
         <v>160</v>
       </c>
       <c r="D53" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B54" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C54" s="10">
         <v>210</v>
       </c>
       <c r="D54" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B55" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C55" s="10">
         <v>240</v>
       </c>
       <c r="D55" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" ht="16.5" customHeight="1" spans="1:4">
@@ -3367,7 +3469,7 @@
         <v>37</v>
       </c>
       <c r="C56" s="12">
-        <f xml:space="preserve">SUM(C44:C55)</f>
+        <f>SUM(C44:C55)</f>
         <v>1991.25</v>
       </c>
     </row>
@@ -3384,13 +3486,13 @@
         <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C59" s="10">
         <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3398,13 +3500,13 @@
         <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C60" s="10">
         <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3412,13 +3514,13 @@
         <v>40</v>
       </c>
       <c r="B61" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C61" s="10">
         <v>40.5</v>
       </c>
       <c r="D61" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3426,13 +3528,13 @@
         <v>40</v>
       </c>
       <c r="B62" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C62" s="10">
         <v>109</v>
       </c>
       <c r="D62" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3440,13 +3542,13 @@
         <v>40</v>
       </c>
       <c r="B63" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C63" s="10">
         <v>48</v>
       </c>
       <c r="D63" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3454,13 +3556,13 @@
         <v>40</v>
       </c>
       <c r="B64" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C64" s="10">
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3468,13 +3570,13 @@
         <v>40</v>
       </c>
       <c r="B65" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C65" s="10">
         <v>10</v>
       </c>
       <c r="D65" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="66" ht="16.5" customHeight="1" spans="1:4">
@@ -3482,22 +3584,22 @@
         <v>39</v>
       </c>
       <c r="C66" s="12">
-        <f xml:space="preserve">SUM(C59:C65)</f>
+        <f>SUM(C59:C65)</f>
         <v>276.5</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" spans="1:4">
       <c r="B68" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C68" s="13">
-        <f xml:space="preserve">C18+C41+C56+C66</f>
+        <f>C18+C41+C56+C66</f>
         <v>6455.7</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1" spans="1:4">
       <c r="A70" s="14" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:4">
@@ -3524,198 +3626,198 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B73" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C73" s="10">
         <v>85.5</v>
       </c>
       <c r="D73" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B74" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C74" s="10">
         <v>161.5</v>
       </c>
       <c r="D74" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B75" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C75" s="10">
         <v>123.5</v>
       </c>
       <c r="D75" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B76" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C76" s="10">
         <v>9.5</v>
       </c>
       <c r="D76" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B77" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C77" s="10">
         <v>115</v>
       </c>
       <c r="D77" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B78" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C78" s="10">
         <v>9.5</v>
       </c>
       <c r="D78" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B79" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C79" s="10">
         <v>133</v>
       </c>
       <c r="D79" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B80" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C80" s="10">
         <v>66.5</v>
       </c>
       <c r="D80" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B81" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C81" s="10">
         <v>14.5</v>
       </c>
       <c r="D81" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B82" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C82" s="10">
         <v>14.5</v>
       </c>
       <c r="D82" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B83" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C83" s="10">
         <v>9.5</v>
       </c>
       <c r="D83" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B84" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C84" s="10">
         <v>9.5</v>
       </c>
       <c r="D84" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B85" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C85" s="10">
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B86" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C86" s="10">
         <v>9.5</v>
       </c>
       <c r="D86" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="87" ht="16.5" customHeight="1" spans="1:4">
@@ -3723,7 +3825,7 @@
         <v>52</v>
       </c>
       <c r="C87" s="12">
-        <f xml:space="preserve">SUM(C73:C86)</f>
+        <f>SUM(C73:C86)</f>
         <v>775.5</v>
       </c>
     </row>
@@ -3740,13 +3842,13 @@
         <v>54</v>
       </c>
       <c r="B90" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C90" s="10">
         <v>202</v>
       </c>
       <c r="D90" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3754,13 +3856,13 @@
         <v>54</v>
       </c>
       <c r="B91" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C91" s="10">
         <v>67.45</v>
       </c>
       <c r="D91" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3768,13 +3870,13 @@
         <v>54</v>
       </c>
       <c r="B92" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C92" s="10">
         <v>67.45</v>
       </c>
       <c r="D92" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3782,13 +3884,13 @@
         <v>54</v>
       </c>
       <c r="B93" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C93" s="10">
         <v>66.78</v>
       </c>
       <c r="D93" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3796,13 +3898,13 @@
         <v>54</v>
       </c>
       <c r="B94" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C94" s="10">
         <v>66.78</v>
       </c>
       <c r="D94" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3810,13 +3912,13 @@
         <v>54</v>
       </c>
       <c r="B95" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C95" s="10">
         <v>66.02</v>
       </c>
       <c r="D95" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3824,13 +3926,13 @@
         <v>54</v>
       </c>
       <c r="B96" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C96" s="10">
         <v>65.55</v>
       </c>
       <c r="D96" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3838,13 +3940,13 @@
         <v>54</v>
       </c>
       <c r="B97" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C97" s="10">
         <v>66.02</v>
       </c>
       <c r="D97" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3852,13 +3954,13 @@
         <v>54</v>
       </c>
       <c r="B98" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C98" s="10">
         <v>69.2</v>
       </c>
       <c r="D98" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3866,13 +3968,13 @@
         <v>54</v>
       </c>
       <c r="B99" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C99" s="10">
         <v>68</v>
       </c>
       <c r="D99" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3880,13 +3982,13 @@
         <v>54</v>
       </c>
       <c r="B100" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C100" s="10">
         <v>41</v>
       </c>
       <c r="D100" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3894,13 +3996,13 @@
         <v>54</v>
       </c>
       <c r="B101" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C101" s="10">
         <v>67.7</v>
       </c>
       <c r="D101" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3908,13 +4010,13 @@
         <v>54</v>
       </c>
       <c r="B102" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C102" s="10">
         <v>68</v>
       </c>
       <c r="D102" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3922,13 +4024,13 @@
         <v>54</v>
       </c>
       <c r="B103" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C103" s="10">
         <v>41.82</v>
       </c>
       <c r="D103" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3936,13 +4038,13 @@
         <v>54</v>
       </c>
       <c r="B104" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C104" s="10">
         <v>197</v>
       </c>
       <c r="D104" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3950,13 +4052,13 @@
         <v>54</v>
       </c>
       <c r="B105" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C105" s="10">
         <v>25.84</v>
       </c>
       <c r="D105" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3964,13 +4066,13 @@
         <v>54</v>
       </c>
       <c r="B106" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C106" s="10">
         <v>191.9</v>
       </c>
       <c r="D106" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3978,13 +4080,13 @@
         <v>54</v>
       </c>
       <c r="B107" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C107" s="10">
         <v>111</v>
       </c>
       <c r="D107" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3992,13 +4094,13 @@
         <v>54</v>
       </c>
       <c r="B108" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C108" s="10">
         <v>65</v>
       </c>
       <c r="D108" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -4006,36 +4108,36 @@
         <v>54</v>
       </c>
       <c r="B109" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C109" s="10">
         <v>65</v>
       </c>
       <c r="D109" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="110" ht="16.5" customHeight="1" spans="1:4">
       <c r="B110" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C110" s="12">
-        <f xml:space="preserve">SUM(C90:C109)</f>
+        <f>SUM(C90:C109)</f>
         <v>1679.51</v>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1" spans="1:4">
       <c r="B112" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C112" s="13">
-        <f xml:space="preserve">C87+C110</f>
+        <f>C87+C110</f>
         <v>2455.01</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
